--- a/protected/data/dmd_data/Drug-Type-Mappings.xlsx
+++ b/protected/data/dmd_data/Drug-Type-Mappings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\A+ PROJECT OPENEYES\MEDICATIONS MANAGEMENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3601FCC-56A0-4E95-B0BD-792A9CE1DBA5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2DC853-41DB-41EE-8523-BD38B52498E9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="20850" windowWidth="38565" windowHeight="20835" tabRatio="857" firstSheet="40" activeTab="44" xr2:uid="{239332B0-502E-49FE-8EA2-75D020103C09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="857" firstSheet="6" activeTab="25" xr2:uid="{239332B0-502E-49FE-8EA2-75D020103C09}"/>
   </bookViews>
   <sheets>
     <sheet name="Analgesic" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <sheet name="Mydriatic" sheetId="25" r:id="rId23"/>
     <sheet name="Non-steroidal Anti-inflammatory" sheetId="26" r:id="rId24"/>
     <sheet name="Steroid" sheetId="27" r:id="rId25"/>
-    <sheet name="Sulfonamides" sheetId="48" r:id="rId26"/>
+    <sheet name="Sulphonamides" sheetId="48" r:id="rId26"/>
     <sheet name="Tear Film Substitute" sheetId="11" r:id="rId27"/>
     <sheet name="Vasoconstrictor" sheetId="28" r:id="rId28"/>
     <sheet name="Viscosurgical" sheetId="29" r:id="rId29"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="795">
   <si>
     <t>Term</t>
   </si>
@@ -2448,12 +2448,6 @@
   </si>
   <si>
     <t>36408711000001107</t>
-  </si>
-  <si>
-    <t>Sulfamethoxazole</t>
-  </si>
-  <si>
-    <t>363528007</t>
   </si>
   <si>
     <t>Sulphonamides</t>
@@ -2869,15 +2863,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFCA7993-61D2-400D-90BC-EC69B4BB7BC7}">
   <dimension ref="A1:C52"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="29.15234375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.3828125" customWidth="1"/>
-    <col min="4" max="4" width="21.15234375" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2888,7 +2882,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2899,7 +2893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2910,7 +2904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2921,7 +2915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2932,7 +2926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2943,7 +2937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2954,7 +2948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2965,7 +2959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2976,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2987,7 +2981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -2998,7 +2992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -3009,7 +3003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -3017,7 +3011,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -3028,7 +3022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -3039,7 +3033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -3050,7 +3044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -3061,7 +3055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -3072,7 +3066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -3083,7 +3077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -3094,7 +3088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -3105,7 +3099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -3116,7 +3110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -3127,7 +3121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -3138,7 +3132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -3149,7 +3143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>59</v>
       </c>
@@ -3160,7 +3154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -3171,7 +3165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -3182,7 +3176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -3193,7 +3187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -3204,7 +3198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -3215,7 +3209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -3226,7 +3220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -3237,7 +3231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -3248,7 +3242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -3259,7 +3253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -3270,7 +3264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -3281,7 +3275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>71</v>
       </c>
@@ -3292,7 +3286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -3303,7 +3297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>73</v>
       </c>
@@ -3314,7 +3308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -3325,7 +3319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>75</v>
       </c>
@@ -3336,7 +3330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>76</v>
       </c>
@@ -3347,7 +3341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>77</v>
       </c>
@@ -3358,7 +3352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>78</v>
       </c>
@@ -3369,7 +3363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>79</v>
       </c>
@@ -3380,7 +3374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>80</v>
       </c>
@@ -3391,7 +3385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>81</v>
       </c>
@@ -3402,7 +3396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>82</v>
       </c>
@@ -3413,7 +3407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>83</v>
       </c>
@@ -3424,7 +3418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>84</v>
       </c>
@@ -3435,7 +3429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>85</v>
       </c>
@@ -3455,15 +3449,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B207CE5-DDAB-4CFD-89A5-E36492B3E134}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.15234375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="22.15234375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="29.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" style="6" customWidth="1"/>
     <col min="3" max="3" width="24" style="6" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="6"/>
+    <col min="4" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3474,7 +3468,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>485</v>
       </c>
@@ -3485,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>487</v>
       </c>
@@ -3496,7 +3490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>489</v>
       </c>
@@ -3507,7 +3501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>491</v>
       </c>
@@ -3518,7 +3512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>493</v>
       </c>
@@ -3529,7 +3523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>495</v>
       </c>
@@ -3540,7 +3534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>496</v>
       </c>
@@ -3551,7 +3545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>498</v>
       </c>
@@ -3571,13 +3565,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAC40F9-8B25-4178-B621-FDE4B225838E}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.15234375" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3588,7 +3582,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>127</v>
       </c>
@@ -3599,7 +3593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>113</v>
       </c>
@@ -3610,7 +3604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>501</v>
       </c>
@@ -3621,7 +3615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>502</v>
       </c>
@@ -3632,7 +3626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>504</v>
       </c>
@@ -3643,67 +3637,67 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="6"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="6"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="6"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="6"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="6"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="6"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" s="6"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" s="6"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="6"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="6"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="6"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="6"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="6"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="6"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="6"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="6"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="6"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="6"/>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="6"/>
     </row>
   </sheetData>
@@ -3714,13 +3708,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D5477DA-BF8A-4353-AC18-9C41C691D37B}">
   <dimension ref="A1:C53"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.53515625" customWidth="1"/>
-    <col min="2" max="2" width="19.15234375" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3731,7 +3725,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>316</v>
       </c>
@@ -3742,7 +3736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>318</v>
       </c>
@@ -3753,7 +3747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>320</v>
       </c>
@@ -3764,151 +3758,151 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="5"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="5"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="5"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="5"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="5"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" s="5"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="5"/>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="5"/>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" s="5"/>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="5"/>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="5"/>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" s="5"/>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="5"/>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" s="5"/>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" s="5"/>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" s="5"/>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" s="5"/>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B41" s="5"/>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" s="5"/>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" s="5"/>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B47" s="5"/>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" s="5"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="5"/>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" s="5"/>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="5"/>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="5"/>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="5"/>
     </row>
   </sheetData>
@@ -3920,13 +3914,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23003D10-3DC6-4626-B038-66D9B7FE08B3}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3937,7 +3931,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>196</v>
       </c>
@@ -3948,7 +3942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>197</v>
       </c>
@@ -3959,7 +3953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>198</v>
       </c>
@@ -3970,7 +3964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>199</v>
       </c>
@@ -3981,7 +3975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>200</v>
       </c>
@@ -3992,7 +3986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>201</v>
       </c>
@@ -4003,7 +3997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>202</v>
       </c>
@@ -4014,7 +4008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>203</v>
       </c>
@@ -4025,7 +4019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>204</v>
       </c>
@@ -4036,7 +4030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>205</v>
       </c>
@@ -4047,7 +4041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>229</v>
       </c>
@@ -4058,7 +4052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>230</v>
       </c>
@@ -4069,7 +4063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>232</v>
       </c>
@@ -4080,7 +4074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>233</v>
       </c>
@@ -4091,7 +4085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>234</v>
       </c>
@@ -4102,7 +4096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>235</v>
       </c>
@@ -4113,7 +4107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>236</v>
       </c>
@@ -4124,19 +4118,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
     </row>
   </sheetData>
@@ -4147,14 +4141,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53F70D2-4340-49BE-B183-13F038AF13C4}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.69140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="23.69140625" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="1" max="1" width="30.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4165,7 +4159,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>506</v>
       </c>
@@ -4184,13 +4178,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C12E098-426C-4714-B1EB-82241231EC01}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.69140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4201,7 +4195,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -4212,7 +4206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>759</v>
       </c>
@@ -4223,7 +4217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>122</v>
       </c>
@@ -4234,7 +4228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>761</v>
       </c>
@@ -4245,7 +4239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>778</v>
       </c>
@@ -4256,7 +4250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>769</v>
       </c>
@@ -4267,7 +4261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>771</v>
       </c>
@@ -4278,7 +4272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>765</v>
       </c>
@@ -4289,7 +4283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>773</v>
       </c>
@@ -4300,7 +4294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>767</v>
       </c>
@@ -4311,7 +4305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>780</v>
       </c>
@@ -4322,7 +4316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>123</v>
       </c>
@@ -4333,7 +4327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>124</v>
       </c>
@@ -4344,7 +4338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>782</v>
       </c>
@@ -4355,7 +4349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>784</v>
       </c>
@@ -4366,7 +4360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>776</v>
       </c>
@@ -4377,7 +4371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>125</v>
       </c>
@@ -4400,13 +4394,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2D860E-6815-46F1-ABA7-A4E86B6647E0}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.3046875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4417,7 +4411,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>193</v>
       </c>
@@ -4428,7 +4422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>194</v>
       </c>
@@ -4439,7 +4433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>188</v>
       </c>
@@ -4450,7 +4444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>189</v>
       </c>
@@ -4461,7 +4455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>190</v>
       </c>
@@ -4472,7 +4466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>191</v>
       </c>
@@ -4483,7 +4477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>195</v>
       </c>
@@ -4494,7 +4488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>192</v>
       </c>
@@ -4505,73 +4499,73 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="5"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="5"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" s="5"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="5"/>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="5"/>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" s="5"/>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
     </row>
   </sheetData>
@@ -4585,14 +4579,14 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D0B909-416A-4778-A836-F280C1A05307}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -4603,7 +4597,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>508</v>
       </c>
@@ -4614,7 +4608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>510</v>
       </c>
@@ -4625,7 +4619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>512</v>
       </c>
@@ -4636,7 +4630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>514</v>
       </c>
@@ -4647,7 +4641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>515</v>
       </c>
@@ -4658,7 +4652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>517</v>
       </c>
@@ -4677,13 +4671,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07EC9308-359D-4C1A-B266-EAF6A215C01A}">
   <dimension ref="A1:C54"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.84375" customWidth="1"/>
+    <col min="1" max="1" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4694,7 +4688,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>322</v>
       </c>
@@ -4705,7 +4699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>324</v>
       </c>
@@ -4716,7 +4710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>325</v>
       </c>
@@ -4727,7 +4721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>327</v>
       </c>
@@ -4738,7 +4732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>329</v>
       </c>
@@ -4749,7 +4743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>331</v>
       </c>
@@ -4760,7 +4754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>333</v>
       </c>
@@ -4771,7 +4765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>335</v>
       </c>
@@ -4782,7 +4776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>337</v>
       </c>
@@ -4793,7 +4787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>339</v>
       </c>
@@ -4804,7 +4798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>341</v>
       </c>
@@ -4815,7 +4809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>343</v>
       </c>
@@ -4826,7 +4820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>345</v>
       </c>
@@ -4837,7 +4831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>347</v>
       </c>
@@ -4848,7 +4842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>349</v>
       </c>
@@ -4859,7 +4853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>351</v>
       </c>
@@ -4870,7 +4864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>353</v>
       </c>
@@ -4881,7 +4875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>355</v>
       </c>
@@ -4892,7 +4886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>357</v>
       </c>
@@ -4903,7 +4897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>359</v>
       </c>
@@ -4914,7 +4908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>361</v>
       </c>
@@ -4925,7 +4919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>362</v>
       </c>
@@ -4936,7 +4930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>364</v>
       </c>
@@ -4947,7 +4941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>366</v>
       </c>
@@ -4958,7 +4952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>368</v>
       </c>
@@ -4969,7 +4963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>369</v>
       </c>
@@ -4980,7 +4974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>371</v>
       </c>
@@ -4991,7 +4985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>558</v>
       </c>
@@ -5000,79 +4994,79 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31" s="5"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="5"/>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="5"/>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" s="5"/>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="5"/>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" s="5"/>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" s="5"/>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" s="5"/>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" s="5"/>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B41" s="5"/>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" s="5"/>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" s="5"/>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B47" s="5"/>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" s="5"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="5"/>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" s="5"/>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="5"/>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="5"/>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B54" s="5"/>
     </row>
   </sheetData>
@@ -5083,14 +5077,14 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C792184D-41FD-437B-AD0E-5F8A4D8304E5}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.84375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="22.3046875" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="1" max="1" width="26.85546875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5101,7 +5095,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>519</v>
       </c>
@@ -5112,7 +5106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>521</v>
       </c>
@@ -5123,7 +5117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>523</v>
       </c>
@@ -5134,7 +5128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>525</v>
       </c>
@@ -5145,7 +5139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>527</v>
       </c>
@@ -5156,7 +5150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>529</v>
       </c>
@@ -5167,7 +5161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>531</v>
       </c>
@@ -5186,13 +5180,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A401CE5B-7F14-4A7E-89FD-7D66914FE703}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.3828125" customWidth="1"/>
-    <col min="2" max="2" width="19.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5203,7 +5197,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -5214,7 +5208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -5225,7 +5219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -5236,7 +5230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5247,7 +5241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -5258,7 +5252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -5269,7 +5263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -5280,7 +5274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -5291,7 +5285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -5302,7 +5296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -5313,7 +5307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -5324,7 +5318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -5335,7 +5329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -5346,7 +5340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -5357,7 +5351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -5368,7 +5362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -5379,7 +5373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -5390,7 +5384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -5401,7 +5395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -5412,7 +5406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -5423,7 +5417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -5434,7 +5428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -5445,7 +5439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -5456,7 +5450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -5467,7 +5461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -5478,7 +5472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -5489,7 +5483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -5500,7 +5494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -5511,7 +5505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -5522,7 +5516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -5533,7 +5527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -5552,14 +5546,14 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D03E0C-BC46-4105-868D-B570CED3B8BA}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.15234375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="21.15234375" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="1" max="1" width="30.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5570,7 +5564,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>533</v>
       </c>
@@ -5581,7 +5575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>535</v>
       </c>
@@ -5592,7 +5586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>537</v>
       </c>
@@ -5603,7 +5597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>539</v>
       </c>
@@ -5614,7 +5608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>541</v>
       </c>
@@ -5625,7 +5619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>190</v>
       </c>
@@ -5636,7 +5630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>544</v>
       </c>
@@ -5647,7 +5641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>546</v>
       </c>
@@ -5658,7 +5652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>548</v>
       </c>
@@ -5669,7 +5663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>551</v>
       </c>
@@ -5688,12 +5682,12 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F0A32FB-3573-434F-82E9-31862C87FCC1}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.53515625" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5704,7 +5698,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>88</v>
       </c>
@@ -5712,7 +5706,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>90</v>
       </c>
@@ -5720,7 +5714,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -5728,7 +5722,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -5736,7 +5730,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>93</v>
       </c>
@@ -5744,7 +5738,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>704</v>
       </c>
@@ -5752,7 +5746,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>92</v>
       </c>
@@ -5760,7 +5754,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>705</v>
       </c>
@@ -5768,7 +5762,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>706</v>
       </c>
@@ -5785,14 +5779,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8417EC00-AE0C-496A-A9AE-3237FBD9E89E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.53515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="41.5703125" style="6" customWidth="1"/>
     <col min="2" max="2" width="20" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5803,7 +5797,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>552</v>
       </c>
@@ -5814,7 +5808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>359</v>
       </c>
@@ -5825,7 +5819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>554</v>
       </c>
@@ -5836,7 +5830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>556</v>
       </c>
@@ -5856,14 +5850,14 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE7324F-E8B2-4B78-A413-F63A7AFAD8AF}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="58.69140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5874,7 +5868,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>559</v>
       </c>
@@ -5885,7 +5879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>561</v>
       </c>
@@ -5896,7 +5890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>563</v>
       </c>
@@ -5907,7 +5901,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>565</v>
       </c>
@@ -5918,7 +5912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>567</v>
       </c>
@@ -5929,7 +5923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>569</v>
       </c>
@@ -5940,7 +5934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>571</v>
       </c>
@@ -5951,7 +5945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>573</v>
       </c>
@@ -5962,7 +5956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>575</v>
       </c>
@@ -5973,7 +5967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>577</v>
       </c>
@@ -5984,7 +5978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>579</v>
       </c>
@@ -5995,7 +5989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>581</v>
       </c>
@@ -6006,7 +6000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>583</v>
       </c>
@@ -6017,7 +6011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>585</v>
       </c>
@@ -6028,7 +6022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>587</v>
       </c>
@@ -6039,7 +6033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>589</v>
       </c>
@@ -6050,7 +6044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>591</v>
       </c>
@@ -6061,7 +6055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>593</v>
       </c>
@@ -6072,7 +6066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>595</v>
       </c>
@@ -6083,7 +6077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>597</v>
       </c>
@@ -6094,7 +6088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>599</v>
       </c>
@@ -6105,7 +6099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>601</v>
       </c>
@@ -6116,7 +6110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>603</v>
       </c>
@@ -6127,7 +6121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>605</v>
       </c>
@@ -6138,7 +6132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>607</v>
       </c>
@@ -6158,14 +6152,14 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DDC9D84-6773-47CD-B699-F79220884C02}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.3828125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.15234375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="1" max="1" width="30.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -6176,7 +6170,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>609</v>
       </c>
@@ -6187,7 +6181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>611</v>
       </c>
@@ -6198,7 +6192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>613</v>
       </c>
@@ -6209,7 +6203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>615</v>
       </c>
@@ -6220,7 +6214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>617</v>
       </c>
@@ -6231,7 +6225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>80</v>
       </c>
@@ -6242,7 +6236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>25</v>
       </c>
@@ -6253,7 +6247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
@@ -6264,7 +6258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>621</v>
       </c>
@@ -6275,7 +6269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>623</v>
       </c>
@@ -6286,7 +6280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>625</v>
       </c>
@@ -6297,7 +6291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>30</v>
       </c>
@@ -6316,15 +6310,15 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA87202-7BD3-4EB8-97E3-6CC639D40E09}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.15234375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="18.15234375" style="6" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="6"/>
+    <col min="2" max="2" width="24.140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" style="6" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -6335,7 +6329,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>628</v>
       </c>
@@ -6346,7 +6340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>630</v>
       </c>
@@ -6357,7 +6351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>632</v>
       </c>
@@ -6368,7 +6362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>634</v>
       </c>
@@ -6379,7 +6373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>636</v>
       </c>
@@ -6390,7 +6384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>638</v>
       </c>
@@ -6401,7 +6395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>640</v>
       </c>
@@ -6412,7 +6406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>642</v>
       </c>
@@ -6423,7 +6417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>644</v>
       </c>
@@ -6434,7 +6428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>646</v>
       </c>
@@ -6445,7 +6439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>648</v>
       </c>
@@ -6456,7 +6450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>650</v>
       </c>
@@ -6467,7 +6461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>652</v>
       </c>
@@ -6478,7 +6472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>654</v>
       </c>
@@ -6489,7 +6483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>656</v>
       </c>
@@ -6500,7 +6494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>658</v>
       </c>
@@ -6511,7 +6505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>660</v>
       </c>
@@ -6522,7 +6516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>662</v>
       </c>
@@ -6541,14 +6535,14 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10121D64-E7C6-4CE1-84F9-0D1E2A3D933D}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.69140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6559,7 +6553,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>140</v>
       </c>
@@ -6567,17 +6561,6 @@
         <v>216</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>791</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>792</v>
-      </c>
-      <c r="C3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6590,13 +6573,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{281080C6-1394-4C69-8511-3E7D104B9199}">
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="67.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.84375" customWidth="1"/>
+    <col min="1" max="1" width="67.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6607,7 +6590,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>237</v>
       </c>
@@ -6618,7 +6601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>238</v>
       </c>
@@ -6629,7 +6612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>240</v>
       </c>
@@ -6640,7 +6623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>241</v>
       </c>
@@ -6651,7 +6634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>243</v>
       </c>
@@ -6662,7 +6645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>244</v>
       </c>
@@ -6673,7 +6656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>245</v>
       </c>
@@ -6684,7 +6667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>246</v>
       </c>
@@ -6695,7 +6678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>249</v>
       </c>
@@ -6706,7 +6689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>251</v>
       </c>
@@ -6717,7 +6700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>252</v>
       </c>
@@ -6728,7 +6711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>254</v>
       </c>
@@ -6739,7 +6722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>256</v>
       </c>
@@ -6750,7 +6733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>258</v>
       </c>
@@ -6761,7 +6744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>260</v>
       </c>
@@ -6772,7 +6755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>262</v>
       </c>
@@ -6783,7 +6766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>264</v>
       </c>
@@ -6794,7 +6777,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>266</v>
       </c>
@@ -6805,7 +6788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>268</v>
       </c>
@@ -6816,7 +6799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>271</v>
       </c>
@@ -6827,7 +6810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>272</v>
       </c>
@@ -6838,7 +6821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>274</v>
       </c>
@@ -6849,7 +6832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>277</v>
       </c>
@@ -6860,7 +6843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>278</v>
       </c>
@@ -6871,7 +6854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>281</v>
       </c>
@@ -6882,7 +6865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>282</v>
       </c>
@@ -6893,7 +6876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>284</v>
       </c>
@@ -6904,7 +6887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>286</v>
       </c>
@@ -6915,7 +6898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>288</v>
       </c>
@@ -6926,7 +6909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>290</v>
       </c>
@@ -6937,7 +6920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>292</v>
       </c>
@@ -6948,7 +6931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>294</v>
       </c>
@@ -6959,7 +6942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>297</v>
       </c>
@@ -6970,7 +6953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>298</v>
       </c>
@@ -6981,7 +6964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>301</v>
       </c>
@@ -6992,7 +6975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>302</v>
       </c>
@@ -7003,7 +6986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>304</v>
       </c>
@@ -7014,7 +6997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>306</v>
       </c>
@@ -7025,7 +7008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>309</v>
       </c>
@@ -7036,7 +7019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>310</v>
       </c>
@@ -7047,7 +7030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>312</v>
       </c>
@@ -7058,7 +7041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>315</v>
       </c>
@@ -7069,7 +7052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B44" s="6"/>
     </row>
   </sheetData>
@@ -7080,14 +7063,14 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3D2916-3F1E-40A9-9FC2-C716E6DCD22F}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.3046875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="2" max="2" width="18.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -7098,7 +7081,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>664</v>
       </c>
@@ -7109,7 +7092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>666</v>
       </c>
@@ -7120,7 +7103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>668</v>
       </c>
@@ -7139,14 +7122,14 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBFE3D3D-FD01-46A3-B15D-C26A0AB7CB2D}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.3046875" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="2" max="2" width="20.28515625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -7157,7 +7140,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>670</v>
       </c>
@@ -7168,7 +7151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>672</v>
       </c>
@@ -7187,13 +7170,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFFBF13F-0C69-4276-9A2D-DA824263F465}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.84375" customWidth="1"/>
-    <col min="2" max="2" width="28.69140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7204,7 +7187,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>113</v>
       </c>
@@ -7215,7 +7198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>114</v>
       </c>
@@ -7226,7 +7209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>115</v>
       </c>
@@ -7237,7 +7220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
@@ -7256,14 +7239,14 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A29F87-B9D7-477E-A267-74910C65A8B4}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.53515625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="18.3046875" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="1" max="1" width="28.5703125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -7274,7 +7257,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>674</v>
       </c>
@@ -7285,7 +7268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>675</v>
       </c>
@@ -7296,7 +7279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>677</v>
       </c>
@@ -7307,7 +7290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>679</v>
       </c>
@@ -7318,7 +7301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>681</v>
       </c>
@@ -7329,7 +7312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>683</v>
       </c>
@@ -7340,7 +7323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>685</v>
       </c>
@@ -7351,7 +7334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>687</v>
       </c>
@@ -7370,12 +7353,12 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CB2C26-B1CA-416D-A77E-72022AF83F79}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7386,7 +7369,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>689</v>
       </c>
@@ -7394,7 +7377,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>690</v>
       </c>
@@ -7402,7 +7385,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>691</v>
       </c>
@@ -7410,7 +7393,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>696</v>
       </c>
@@ -7418,7 +7401,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>692</v>
       </c>
@@ -7426,7 +7409,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>693</v>
       </c>
@@ -7434,7 +7417,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>694</v>
       </c>
@@ -7442,7 +7425,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>695</v>
       </c>
@@ -7458,13 +7441,13 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB0FA641-5444-49C3-B55E-F21EF4EB15D5}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7475,7 +7458,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>322</v>
       </c>
@@ -7494,13 +7477,13 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0BDB5B-026D-4A03-B8DE-5506D3CD9DFC}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7511,7 +7494,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>708</v>
       </c>
@@ -7530,14 +7513,14 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6BDB288-EA01-4B03-BF53-469D558C2727}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.4609375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7548,7 +7531,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>331</v>
       </c>
@@ -7559,7 +7542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>333</v>
       </c>
@@ -7570,7 +7553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>337</v>
       </c>
@@ -7589,14 +7572,14 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37C1C84A-5310-48CA-BDDE-0FDED6CE9698}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.4609375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7607,7 +7590,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>710</v>
       </c>
@@ -7626,12 +7609,12 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC49E189-8373-41B3-93A1-1588623AC479}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7642,7 +7625,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>763</v>
       </c>
@@ -7658,14 +7641,14 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE143BB2-5AEA-490A-82EC-21B9D0F1DD1D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.4609375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7676,7 +7659,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>510</v>
       </c>
@@ -7687,7 +7670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>512</v>
       </c>
@@ -7698,7 +7681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>514</v>
       </c>
@@ -7717,14 +7700,14 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC204BD-7D3A-4D97-BCEA-C6FC5AE478FD}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.4609375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7735,7 +7718,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>504</v>
       </c>
@@ -7746,7 +7729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>713</v>
       </c>
@@ -7757,7 +7740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>715</v>
       </c>
@@ -7768,7 +7751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>717</v>
       </c>
@@ -7779,7 +7762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>719</v>
       </c>
@@ -7790,7 +7773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>721</v>
       </c>
@@ -7801,7 +7784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>723</v>
       </c>
@@ -7812,7 +7795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>725</v>
       </c>
@@ -7831,12 +7814,12 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27F8D9F-1421-4CC6-8FC1-BFB509BB17ED}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7847,7 +7830,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>707</v>
       </c>
@@ -7863,13 +7846,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172C45E1-A1C9-456B-ABDF-55ABD530AD65}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.69140625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7880,7 +7863,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>151</v>
       </c>
@@ -7891,7 +7874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>117</v>
       </c>
@@ -7902,7 +7885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>118</v>
       </c>
@@ -7913,7 +7896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>174</v>
       </c>
@@ -7924,7 +7907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>119</v>
       </c>
@@ -7935,7 +7918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>171</v>
       </c>
@@ -7946,7 +7929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -7957,7 +7940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>120</v>
       </c>
@@ -7968,7 +7951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>763</v>
       </c>
@@ -7976,7 +7959,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -7987,7 +7970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -7998,7 +7981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>127</v>
       </c>
@@ -8009,7 +7992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -8020,7 +8003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>129</v>
       </c>
@@ -8031,7 +8014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>130</v>
       </c>
@@ -8042,7 +8025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>131</v>
       </c>
@@ -8053,7 +8036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>132</v>
       </c>
@@ -8064,7 +8047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>133</v>
       </c>
@@ -8075,7 +8058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>134</v>
       </c>
@@ -8086,7 +8069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>135</v>
       </c>
@@ -8097,7 +8080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>136</v>
       </c>
@@ -8108,7 +8091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>137</v>
       </c>
@@ -8119,7 +8102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>138</v>
       </c>
@@ -8130,7 +8113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>139</v>
       </c>
@@ -8141,7 +8124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>141</v>
       </c>
@@ -8152,7 +8135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>140</v>
       </c>
@@ -8163,7 +8146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -8174,7 +8157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>143</v>
       </c>
@@ -8185,7 +8168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>144</v>
       </c>
@@ -8196,7 +8179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>146</v>
       </c>
@@ -8207,7 +8190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>147</v>
       </c>
@@ -8218,7 +8201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>148</v>
       </c>
@@ -8229,7 +8212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>149</v>
       </c>
@@ -8240,7 +8223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>150</v>
       </c>
@@ -8251,7 +8234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>160</v>
       </c>
@@ -8262,7 +8245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>152</v>
       </c>
@@ -8273,7 +8256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>161</v>
       </c>
@@ -8284,7 +8267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>169</v>
       </c>
@@ -8295,7 +8278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>210</v>
       </c>
@@ -8306,7 +8289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>180</v>
       </c>
@@ -8317,7 +8300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>153</v>
       </c>
@@ -8328,7 +8311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>162</v>
       </c>
@@ -8339,7 +8322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>163</v>
       </c>
@@ -8350,7 +8333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>164</v>
       </c>
@@ -8361,7 +8344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>165</v>
       </c>
@@ -8372,7 +8355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>166</v>
       </c>
@@ -8383,7 +8366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>167</v>
       </c>
@@ -8394,7 +8377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>168</v>
       </c>
@@ -8405,7 +8388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>154</v>
       </c>
@@ -8416,7 +8399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>155</v>
       </c>
@@ -8427,7 +8410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>170</v>
       </c>
@@ -8438,7 +8421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>156</v>
       </c>
@@ -8449,7 +8432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>172</v>
       </c>
@@ -8460,7 +8443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>173</v>
       </c>
@@ -8471,7 +8454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>175</v>
       </c>
@@ -8482,7 +8465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>176</v>
       </c>
@@ -8493,7 +8476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>177</v>
       </c>
@@ -8504,7 +8487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>178</v>
       </c>
@@ -8515,7 +8498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>179</v>
       </c>
@@ -8526,7 +8509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>157</v>
       </c>
@@ -8537,7 +8520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>181</v>
       </c>
@@ -8548,7 +8531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>158</v>
       </c>
@@ -8559,7 +8542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>182</v>
       </c>
@@ -8570,7 +8553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>183</v>
       </c>
@@ -8581,7 +8564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>184</v>
       </c>
@@ -8592,7 +8575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>159</v>
       </c>
@@ -8603,7 +8586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>185</v>
       </c>
@@ -8614,7 +8597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>186</v>
       </c>
@@ -8625,7 +8608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>187</v>
       </c>
@@ -8649,14 +8632,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC7756C4-8F48-4292-9D5F-608F03982191}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.4609375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8667,7 +8650,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -8678,7 +8661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>728</v>
       </c>
@@ -8689,7 +8672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
@@ -8700,7 +8683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -8711,7 +8694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -8722,7 +8705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>732</v>
       </c>
@@ -8733,7 +8716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -8744,7 +8727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>735</v>
       </c>
@@ -8755,7 +8738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -8766,7 +8749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -8777,7 +8760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -8788,7 +8771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -8799,7 +8782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -8810,7 +8793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>740</v>
       </c>
@@ -8821,7 +8804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>742</v>
       </c>
@@ -8832,7 +8815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>744</v>
       </c>
@@ -8843,7 +8826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>746</v>
       </c>
@@ -8854,7 +8837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -8865,7 +8848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -8876,7 +8859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -8887,7 +8870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>749</v>
       </c>
@@ -8898,7 +8881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>751</v>
       </c>
@@ -8918,14 +8901,14 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31A794ED-D467-4745-8815-1ADB5AAC40B7}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.4609375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8936,7 +8919,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>172</v>
       </c>
@@ -8947,7 +8930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>120</v>
       </c>
@@ -8958,7 +8941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>171</v>
       </c>
@@ -8969,7 +8952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>173</v>
       </c>
@@ -8980,7 +8963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -8991,7 +8974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>174</v>
       </c>
@@ -9010,14 +8993,14 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132418B5-41DA-4B0C-AC22-24FD97EA30D1}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.4609375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9028,7 +9011,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>788</v>
       </c>
@@ -9039,7 +9022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>789</v>
       </c>
@@ -9058,12 +9041,12 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41F98509-ACD5-4B1D-B1F8-47EAFD9F9391}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9074,9 +9057,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C2" t="s">
         <v>45</v>
@@ -9090,14 +9073,14 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10AD3146-C09B-449D-B489-9D8465525A77}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.4609375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9108,12 +9091,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -9127,14 +9110,14 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCE8F63-B951-470B-A6A0-F59BE8BCB360}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.4609375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9145,12 +9128,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>184</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -9164,12 +9147,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC52D35-3C18-4000-AA82-24034B6E78F1}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9180,7 +9163,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>145</v>
       </c>
@@ -9196,13 +9179,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC7C3DA-29D4-4832-A1A6-B0D909B8CCD0}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.53515625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9213,7 +9196,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>112</v>
       </c>
@@ -9224,7 +9207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>110</v>
       </c>
@@ -9235,7 +9218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>101</v>
       </c>
@@ -9246,7 +9229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -9257,7 +9240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -9268,7 +9251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>104</v>
       </c>
@@ -9279,7 +9262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>96</v>
       </c>
@@ -9290,7 +9273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>106</v>
       </c>
@@ -9301,7 +9284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -9312,7 +9295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>102</v>
       </c>
@@ -9323,7 +9306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>107</v>
       </c>
@@ -9334,7 +9317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>103</v>
       </c>
@@ -9345,7 +9328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>98</v>
       </c>
@@ -9356,7 +9339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>99</v>
       </c>
@@ -9367,7 +9350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -9378,7 +9361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>100</v>
       </c>
@@ -9389,7 +9372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>111</v>
       </c>
@@ -9400,7 +9383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>108</v>
       </c>
@@ -9411,7 +9394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>109</v>
       </c>
@@ -9434,13 +9417,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C3E711-E739-45ED-AA8D-7AF2B03BB8CE}">
   <dimension ref="A1:C73"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.69140625" customWidth="1"/>
+    <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9451,7 +9434,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>373</v>
       </c>
@@ -9462,7 +9445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>375</v>
       </c>
@@ -9473,7 +9456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>377</v>
       </c>
@@ -9484,7 +9467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>379</v>
       </c>
@@ -9495,7 +9478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>381</v>
       </c>
@@ -9506,7 +9489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>383</v>
       </c>
@@ -9517,7 +9500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>385</v>
       </c>
@@ -9528,7 +9511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>386</v>
       </c>
@@ -9539,7 +9522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>388</v>
       </c>
@@ -9550,7 +9533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>390</v>
       </c>
@@ -9561,7 +9544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>392</v>
       </c>
@@ -9572,7 +9555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>394</v>
       </c>
@@ -9583,7 +9566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>396</v>
       </c>
@@ -9594,7 +9577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>398</v>
       </c>
@@ -9605,7 +9588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>400</v>
       </c>
@@ -9616,7 +9599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>402</v>
       </c>
@@ -9627,7 +9610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>404</v>
       </c>
@@ -9638,7 +9621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>406</v>
       </c>
@@ -9649,7 +9632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>408</v>
       </c>
@@ -9660,7 +9643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>410</v>
       </c>
@@ -9671,7 +9654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>413</v>
       </c>
@@ -9682,7 +9665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>414</v>
       </c>
@@ -9693,7 +9676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>416</v>
       </c>
@@ -9704,7 +9687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>418</v>
       </c>
@@ -9715,7 +9698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>420</v>
       </c>
@@ -9726,7 +9709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>422</v>
       </c>
@@ -9737,232 +9720,232 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -9976,14 +9959,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E17311-B226-4FC3-B5D4-D46E3B37B0BC}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.3046875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="18.84375" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="1" max="1" width="26.28515625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -9994,7 +9977,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>424</v>
       </c>
@@ -10005,7 +9988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>426</v>
       </c>
@@ -10016,7 +9999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>428</v>
       </c>
@@ -10027,7 +10010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>430</v>
       </c>
@@ -10038,7 +10021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>432</v>
       </c>
@@ -10057,14 +10040,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C7765BD-8B47-4845-8E4B-54BCF383938E}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.53515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.3046875" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="9.15234375" style="6"/>
+    <col min="1" max="1" width="53.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -10075,7 +10058,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>434</v>
       </c>
@@ -10086,7 +10069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>436</v>
       </c>
@@ -10097,7 +10080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>438</v>
       </c>
@@ -10108,7 +10091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>440</v>
       </c>
@@ -10119,7 +10102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>442</v>
       </c>
@@ -10130,7 +10113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>444</v>
       </c>
@@ -10141,7 +10124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>446</v>
       </c>
@@ -10152,7 +10135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>449</v>
       </c>
@@ -10163,7 +10146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>450</v>
       </c>
@@ -10174,7 +10157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>452</v>
       </c>
@@ -10185,7 +10168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>454</v>
       </c>
@@ -10196,7 +10179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>456</v>
       </c>
@@ -10207,7 +10190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>113</v>
       </c>
@@ -10218,7 +10201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>459</v>
       </c>
@@ -10229,7 +10212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>461</v>
       </c>
@@ -10240,7 +10223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>463</v>
       </c>
@@ -10251,7 +10234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>465</v>
       </c>
@@ -10262,7 +10245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>467</v>
       </c>
@@ -10273,7 +10256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>469</v>
       </c>
@@ -10284,7 +10267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>471</v>
       </c>
@@ -10295,7 +10278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>473</v>
       </c>
@@ -10306,7 +10289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>475</v>
       </c>
@@ -10317,7 +10300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>477</v>
       </c>
@@ -10328,7 +10311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>479</v>
       </c>
@@ -10339,7 +10322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>481</v>
       </c>
@@ -10350,7 +10333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>483</v>
       </c>

--- a/protected/data/dmd_data/Drug-Type-Mappings.xlsx
+++ b/protected/data/dmd_data/Drug-Type-Mappings.xlsx
@@ -8,56 +8,57 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c58bff20204d3898/Documents/docker-compose/MM/dmd_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_611EE3B2B6AEC4E91FAFF6C24585CFD48B53695D" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{55C6BD87-7413-4F32-8CAD-30DDE2A6561E}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_611EE3B2B6AEC4E91FAFF6C24585CFD48B53695D" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{1884293B-2C79-480C-ACA6-99C33C7B34BC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="750" firstSheet="16" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="750" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Non-opioid Analgesic" sheetId="1" r:id="rId1"/>
-    <sheet name="Analgesic" sheetId="2" r:id="rId2"/>
-    <sheet name="Antiamoebic" sheetId="3" r:id="rId3"/>
-    <sheet name="Cephalosporins" sheetId="4" r:id="rId4"/>
-    <sheet name="Antibacterial" sheetId="5" r:id="rId5"/>
-    <sheet name="Antibiotic" sheetId="6" r:id="rId6"/>
-    <sheet name="Anticoagulant" sheetId="7" r:id="rId7"/>
-    <sheet name="Antidiabetic" sheetId="8" r:id="rId8"/>
-    <sheet name="Antiemetic" sheetId="9" r:id="rId9"/>
-    <sheet name="Antifungal" sheetId="10" r:id="rId10"/>
-    <sheet name="Antihistamine" sheetId="11" r:id="rId11"/>
-    <sheet name="Antiseptic" sheetId="12" r:id="rId12"/>
-    <sheet name="AntiVEGF" sheetId="13" r:id="rId13"/>
-    <sheet name="Antiviral" sheetId="14" r:id="rId14"/>
-    <sheet name="Contact Lens Solution" sheetId="15" r:id="rId15"/>
-    <sheet name="Cytotoxic" sheetId="16" r:id="rId16"/>
-    <sheet name="Dye" sheetId="17" r:id="rId17"/>
-    <sheet name="Glaucoma" sheetId="18" r:id="rId18"/>
-    <sheet name="Hypnotic" sheetId="19" r:id="rId19"/>
-    <sheet name="Immunosuppresive" sheetId="20" r:id="rId20"/>
-    <sheet name="Ophthalmic" sheetId="21" r:id="rId21"/>
-    <sheet name="Miotic" sheetId="22" r:id="rId22"/>
-    <sheet name="Mydriatic" sheetId="23" r:id="rId23"/>
-    <sheet name="Non-steroidal Anti-inflammatory" sheetId="24" r:id="rId24"/>
-    <sheet name="Steroid" sheetId="25" r:id="rId25"/>
-    <sheet name="Sulphonamides" sheetId="26" r:id="rId26"/>
-    <sheet name="Tear Film Substitute" sheetId="27" r:id="rId27"/>
-    <sheet name="Vasoconstrictor" sheetId="28" r:id="rId28"/>
-    <sheet name="Viscosurgical" sheetId="29" r:id="rId29"/>
-    <sheet name="Alphablocker" sheetId="30" r:id="rId30"/>
-    <sheet name="medication_management" sheetId="31" r:id="rId31"/>
-    <sheet name="Allergy_Acetazolamide" sheetId="32" r:id="rId32"/>
-    <sheet name="Allergy_Atropine" sheetId="33" r:id="rId33"/>
-    <sheet name="Allergy_Brimonidine" sheetId="34" r:id="rId34"/>
-    <sheet name="Allergy_Carbamezapine" sheetId="35" r:id="rId35"/>
-    <sheet name="Allergy_Cephalosporins" sheetId="36" r:id="rId36"/>
-    <sheet name="Allergy_Fluorescein" sheetId="37" r:id="rId37"/>
-    <sheet name="Allergy_Iodine" sheetId="38" r:id="rId38"/>
-    <sheet name="Allergy_NSAIDs" sheetId="39" r:id="rId39"/>
-    <sheet name="Allergy_Opiates" sheetId="40" r:id="rId40"/>
-    <sheet name="Allergy_Penicillin" sheetId="41" r:id="rId41"/>
-    <sheet name="Allergy_Phenytoin" sheetId="42" r:id="rId42"/>
-    <sheet name="Allergy_Sulphonamides" sheetId="43" r:id="rId43"/>
-    <sheet name="Allergy_Suxamethonium" sheetId="44" r:id="rId44"/>
-    <sheet name="Allergy_Tetracycline" sheetId="45" r:id="rId45"/>
+    <sheet name="Simple Analgesics" sheetId="46" r:id="rId2"/>
+    <sheet name="Analgesic" sheetId="2" r:id="rId3"/>
+    <sheet name="Antiamoebic" sheetId="3" r:id="rId4"/>
+    <sheet name="Cephalosporins" sheetId="4" r:id="rId5"/>
+    <sheet name="Antibacterial" sheetId="5" r:id="rId6"/>
+    <sheet name="Antibiotic" sheetId="6" r:id="rId7"/>
+    <sheet name="Anticoagulant" sheetId="7" r:id="rId8"/>
+    <sheet name="Antidiabetic" sheetId="8" r:id="rId9"/>
+    <sheet name="Antiemetic" sheetId="9" r:id="rId10"/>
+    <sheet name="Antifungal" sheetId="10" r:id="rId11"/>
+    <sheet name="Antihistamine" sheetId="11" r:id="rId12"/>
+    <sheet name="Antiseptic" sheetId="12" r:id="rId13"/>
+    <sheet name="AntiVEGF" sheetId="13" r:id="rId14"/>
+    <sheet name="Antiviral" sheetId="14" r:id="rId15"/>
+    <sheet name="Contact Lens Solution" sheetId="15" r:id="rId16"/>
+    <sheet name="Cytotoxic" sheetId="16" r:id="rId17"/>
+    <sheet name="Dye" sheetId="17" r:id="rId18"/>
+    <sheet name="Glaucoma" sheetId="18" r:id="rId19"/>
+    <sheet name="Hypnotic" sheetId="19" r:id="rId20"/>
+    <sheet name="Immunosuppresive" sheetId="20" r:id="rId21"/>
+    <sheet name="Ophthalmic" sheetId="21" r:id="rId22"/>
+    <sheet name="Miotic" sheetId="22" r:id="rId23"/>
+    <sheet name="Mydriatic" sheetId="23" r:id="rId24"/>
+    <sheet name="Non-steroidal Anti-inflammatory" sheetId="24" r:id="rId25"/>
+    <sheet name="Steroid" sheetId="25" r:id="rId26"/>
+    <sheet name="Sulphonamides" sheetId="26" r:id="rId27"/>
+    <sheet name="Tear Film Substitute" sheetId="27" r:id="rId28"/>
+    <sheet name="Vasoconstrictor" sheetId="28" r:id="rId29"/>
+    <sheet name="Viscosurgical" sheetId="29" r:id="rId30"/>
+    <sheet name="Alphablocker" sheetId="30" r:id="rId31"/>
+    <sheet name="medication_management" sheetId="31" r:id="rId32"/>
+    <sheet name="Allergy_Acetazolamide" sheetId="32" r:id="rId33"/>
+    <sheet name="Allergy_Atropine" sheetId="33" r:id="rId34"/>
+    <sheet name="Allergy_Brimonidine" sheetId="34" r:id="rId35"/>
+    <sheet name="Allergy_Carbamezapine" sheetId="35" r:id="rId36"/>
+    <sheet name="Allergy_Cephalosporins" sheetId="36" r:id="rId37"/>
+    <sheet name="Allergy_Fluorescein" sheetId="37" r:id="rId38"/>
+    <sheet name="Allergy_Iodine" sheetId="38" r:id="rId39"/>
+    <sheet name="Allergy_NSAIDs" sheetId="39" r:id="rId40"/>
+    <sheet name="Allergy_Opiates" sheetId="40" r:id="rId41"/>
+    <sheet name="Allergy_Penicillin" sheetId="41" r:id="rId42"/>
+    <sheet name="Allergy_Phenytoin" sheetId="42" r:id="rId43"/>
+    <sheet name="Allergy_Sulphonamides" sheetId="43" r:id="rId44"/>
+    <sheet name="Allergy_Suxamethonium" sheetId="44" r:id="rId45"/>
+    <sheet name="Allergy_Tetracycline" sheetId="45" r:id="rId46"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="786">
   <si>
     <t>Term</t>
   </si>
@@ -1775,12 +1776,6 @@
     <t>11847009</t>
   </si>
   <si>
-    <t>Misoprostol + Naproxen</t>
-  </si>
-  <si>
-    <t>346577003</t>
-  </si>
-  <si>
     <t>Naproxen + Esomeprazole</t>
   </si>
   <si>
@@ -2430,6 +2425,9 @@
   </si>
   <si>
     <t>Viscosurgical</t>
+  </si>
+  <si>
+    <t>Simple Analgesics</t>
   </si>
 </sst>
 </file>
@@ -3262,6 +3260,88 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:AMK6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" style="2" customWidth="1"/>
+    <col min="3" max="1025" width="9.140625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AMK25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3552,7 +3632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AMK9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3668,7 +3748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3813,7 +3893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4020,7 +4100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4216,7 +4296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:AMK2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4254,7 +4334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4438,7 +4518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:AMK7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4531,7 +4611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4939,7 +5019,2335 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF5A4364-632F-4CC1-AFBE-F1E4AF3F5947}">
+  <dimension ref="A1:AMK25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="1">
+        <v>85990009</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="1">
+        <v>7947003</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="1">
+        <v>412569008</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="1">
+        <v>319357003</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="1">
+        <v>400487008</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="1">
+        <v>400819008</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="1">
+        <v>424102008</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="1">
+        <v>412556009</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="1">
+        <v>90332006</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="1">
+        <v>423037001</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="1">
+        <v>350309002</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="1">
+        <v>423936008</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1025" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1025" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="1">
+        <v>423801005</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1025" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="1">
+        <v>400658001</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1025" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="1">
+        <v>427164001</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1025" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="1">
+        <v>412499001</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1025" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="1">
+        <v>398785002</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1025" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1025" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="2"/>
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AE24" s="2"/>
+      <c r="AF24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="2"/>
+      <c r="AM24" s="2"/>
+      <c r="AN24" s="2"/>
+      <c r="AO24" s="2"/>
+      <c r="AP24" s="2"/>
+      <c r="AQ24" s="2"/>
+      <c r="AR24" s="2"/>
+      <c r="AS24" s="2"/>
+      <c r="AT24" s="2"/>
+      <c r="AU24" s="2"/>
+      <c r="AV24" s="2"/>
+      <c r="AW24" s="2"/>
+      <c r="AX24" s="2"/>
+      <c r="AY24" s="2"/>
+      <c r="AZ24" s="2"/>
+      <c r="BA24" s="2"/>
+      <c r="BB24" s="2"/>
+      <c r="BC24" s="2"/>
+      <c r="BD24" s="2"/>
+      <c r="BE24" s="2"/>
+      <c r="BF24" s="2"/>
+      <c r="BG24" s="2"/>
+      <c r="BH24" s="2"/>
+      <c r="BI24" s="2"/>
+      <c r="BJ24" s="2"/>
+      <c r="BK24" s="2"/>
+      <c r="BL24" s="2"/>
+      <c r="BM24" s="2"/>
+      <c r="BN24" s="2"/>
+      <c r="BO24" s="2"/>
+      <c r="BP24" s="2"/>
+      <c r="BQ24" s="2"/>
+      <c r="BR24" s="2"/>
+      <c r="BS24" s="2"/>
+      <c r="BT24" s="2"/>
+      <c r="BU24" s="2"/>
+      <c r="BV24" s="2"/>
+      <c r="BW24" s="2"/>
+      <c r="BX24" s="2"/>
+      <c r="BY24" s="2"/>
+      <c r="BZ24" s="2"/>
+      <c r="CA24" s="2"/>
+      <c r="CB24" s="2"/>
+      <c r="CC24" s="2"/>
+      <c r="CD24" s="2"/>
+      <c r="CE24" s="2"/>
+      <c r="CF24" s="2"/>
+      <c r="CG24" s="2"/>
+      <c r="CH24" s="2"/>
+      <c r="CI24" s="2"/>
+      <c r="CJ24" s="2"/>
+      <c r="CK24" s="2"/>
+      <c r="CL24" s="2"/>
+      <c r="CM24" s="2"/>
+      <c r="CN24" s="2"/>
+      <c r="CO24" s="2"/>
+      <c r="CP24" s="2"/>
+      <c r="CQ24" s="2"/>
+      <c r="CR24" s="2"/>
+      <c r="CS24" s="2"/>
+      <c r="CT24" s="2"/>
+      <c r="CU24" s="2"/>
+      <c r="CV24" s="2"/>
+      <c r="CW24" s="2"/>
+      <c r="CX24" s="2"/>
+      <c r="CY24" s="2"/>
+      <c r="CZ24" s="2"/>
+      <c r="DA24" s="2"/>
+      <c r="DB24" s="2"/>
+      <c r="DC24" s="2"/>
+      <c r="DD24" s="2"/>
+      <c r="DE24" s="2"/>
+      <c r="DF24" s="2"/>
+      <c r="DG24" s="2"/>
+      <c r="DH24" s="2"/>
+      <c r="DI24" s="2"/>
+      <c r="DJ24" s="2"/>
+      <c r="DK24" s="2"/>
+      <c r="DL24" s="2"/>
+      <c r="DM24" s="2"/>
+      <c r="DN24" s="2"/>
+      <c r="DO24" s="2"/>
+      <c r="DP24" s="2"/>
+      <c r="DQ24" s="2"/>
+      <c r="DR24" s="2"/>
+      <c r="DS24" s="2"/>
+      <c r="DT24" s="2"/>
+      <c r="DU24" s="2"/>
+      <c r="DV24" s="2"/>
+      <c r="DW24" s="2"/>
+      <c r="DX24" s="2"/>
+      <c r="DY24" s="2"/>
+      <c r="DZ24" s="2"/>
+      <c r="EA24" s="2"/>
+      <c r="EB24" s="2"/>
+      <c r="EC24" s="2"/>
+      <c r="ED24" s="2"/>
+      <c r="EE24" s="2"/>
+      <c r="EF24" s="2"/>
+      <c r="EG24" s="2"/>
+      <c r="EH24" s="2"/>
+      <c r="EI24" s="2"/>
+      <c r="EJ24" s="2"/>
+      <c r="EK24" s="2"/>
+      <c r="EL24" s="2"/>
+      <c r="EM24" s="2"/>
+      <c r="EN24" s="2"/>
+      <c r="EO24" s="2"/>
+      <c r="EP24" s="2"/>
+      <c r="EQ24" s="2"/>
+      <c r="ER24" s="2"/>
+      <c r="ES24" s="2"/>
+      <c r="ET24" s="2"/>
+      <c r="EU24" s="2"/>
+      <c r="EV24" s="2"/>
+      <c r="EW24" s="2"/>
+      <c r="EX24" s="2"/>
+      <c r="EY24" s="2"/>
+      <c r="EZ24" s="2"/>
+      <c r="FA24" s="2"/>
+      <c r="FB24" s="2"/>
+      <c r="FC24" s="2"/>
+      <c r="FD24" s="2"/>
+      <c r="FE24" s="2"/>
+      <c r="FF24" s="2"/>
+      <c r="FG24" s="2"/>
+      <c r="FH24" s="2"/>
+      <c r="FI24" s="2"/>
+      <c r="FJ24" s="2"/>
+      <c r="FK24" s="2"/>
+      <c r="FL24" s="2"/>
+      <c r="FM24" s="2"/>
+      <c r="FN24" s="2"/>
+      <c r="FO24" s="2"/>
+      <c r="FP24" s="2"/>
+      <c r="FQ24" s="2"/>
+      <c r="FR24" s="2"/>
+      <c r="FS24" s="2"/>
+      <c r="FT24" s="2"/>
+      <c r="FU24" s="2"/>
+      <c r="FV24" s="2"/>
+      <c r="FW24" s="2"/>
+      <c r="FX24" s="2"/>
+      <c r="FY24" s="2"/>
+      <c r="FZ24" s="2"/>
+      <c r="GA24" s="2"/>
+      <c r="GB24" s="2"/>
+      <c r="GC24" s="2"/>
+      <c r="GD24" s="2"/>
+      <c r="GE24" s="2"/>
+      <c r="GF24" s="2"/>
+      <c r="GG24" s="2"/>
+      <c r="GH24" s="2"/>
+      <c r="GI24" s="2"/>
+      <c r="GJ24" s="2"/>
+      <c r="GK24" s="2"/>
+      <c r="GL24" s="2"/>
+      <c r="GM24" s="2"/>
+      <c r="GN24" s="2"/>
+      <c r="GO24" s="2"/>
+      <c r="GP24" s="2"/>
+      <c r="GQ24" s="2"/>
+      <c r="GR24" s="2"/>
+      <c r="GS24" s="2"/>
+      <c r="GT24" s="2"/>
+      <c r="GU24" s="2"/>
+      <c r="GV24" s="2"/>
+      <c r="GW24" s="2"/>
+      <c r="GX24" s="2"/>
+      <c r="GY24" s="2"/>
+      <c r="GZ24" s="2"/>
+      <c r="HA24" s="2"/>
+      <c r="HB24" s="2"/>
+      <c r="HC24" s="2"/>
+      <c r="HD24" s="2"/>
+      <c r="HE24" s="2"/>
+      <c r="HF24" s="2"/>
+      <c r="HG24" s="2"/>
+      <c r="HH24" s="2"/>
+      <c r="HI24" s="2"/>
+      <c r="HJ24" s="2"/>
+      <c r="HK24" s="2"/>
+      <c r="HL24" s="2"/>
+      <c r="HM24" s="2"/>
+      <c r="HN24" s="2"/>
+      <c r="HO24" s="2"/>
+      <c r="HP24" s="2"/>
+      <c r="HQ24" s="2"/>
+      <c r="HR24" s="2"/>
+      <c r="HS24" s="2"/>
+      <c r="HT24" s="2"/>
+      <c r="HU24" s="2"/>
+      <c r="HV24" s="2"/>
+      <c r="HW24" s="2"/>
+      <c r="HX24" s="2"/>
+      <c r="HY24" s="2"/>
+      <c r="HZ24" s="2"/>
+      <c r="IA24" s="2"/>
+      <c r="IB24" s="2"/>
+      <c r="IC24" s="2"/>
+      <c r="ID24" s="2"/>
+      <c r="IE24" s="2"/>
+      <c r="IF24" s="2"/>
+      <c r="IG24" s="2"/>
+      <c r="IH24" s="2"/>
+      <c r="II24" s="2"/>
+      <c r="IJ24" s="2"/>
+      <c r="IK24" s="2"/>
+      <c r="IL24" s="2"/>
+      <c r="IM24" s="2"/>
+      <c r="IN24" s="2"/>
+      <c r="IO24" s="2"/>
+      <c r="IP24" s="2"/>
+      <c r="IQ24" s="2"/>
+      <c r="IR24" s="2"/>
+      <c r="IS24" s="2"/>
+      <c r="IT24" s="2"/>
+      <c r="IU24" s="2"/>
+      <c r="IV24" s="2"/>
+      <c r="IW24" s="2"/>
+      <c r="IX24" s="2"/>
+      <c r="IY24" s="2"/>
+      <c r="IZ24" s="2"/>
+      <c r="JA24" s="2"/>
+      <c r="JB24" s="2"/>
+      <c r="JC24" s="2"/>
+      <c r="JD24" s="2"/>
+      <c r="JE24" s="2"/>
+      <c r="JF24" s="2"/>
+      <c r="JG24" s="2"/>
+      <c r="JH24" s="2"/>
+      <c r="JI24" s="2"/>
+      <c r="JJ24" s="2"/>
+      <c r="JK24" s="2"/>
+      <c r="JL24" s="2"/>
+      <c r="JM24" s="2"/>
+      <c r="JN24" s="2"/>
+      <c r="JO24" s="2"/>
+      <c r="JP24" s="2"/>
+      <c r="JQ24" s="2"/>
+      <c r="JR24" s="2"/>
+      <c r="JS24" s="2"/>
+      <c r="JT24" s="2"/>
+      <c r="JU24" s="2"/>
+      <c r="JV24" s="2"/>
+      <c r="JW24" s="2"/>
+      <c r="JX24" s="2"/>
+      <c r="JY24" s="2"/>
+      <c r="JZ24" s="2"/>
+      <c r="KA24" s="2"/>
+      <c r="KB24" s="2"/>
+      <c r="KC24" s="2"/>
+      <c r="KD24" s="2"/>
+      <c r="KE24" s="2"/>
+      <c r="KF24" s="2"/>
+      <c r="KG24" s="2"/>
+      <c r="KH24" s="2"/>
+      <c r="KI24" s="2"/>
+      <c r="KJ24" s="2"/>
+      <c r="KK24" s="2"/>
+      <c r="KL24" s="2"/>
+      <c r="KM24" s="2"/>
+      <c r="KN24" s="2"/>
+      <c r="KO24" s="2"/>
+      <c r="KP24" s="2"/>
+      <c r="KQ24" s="2"/>
+      <c r="KR24" s="2"/>
+      <c r="KS24" s="2"/>
+      <c r="KT24" s="2"/>
+      <c r="KU24" s="2"/>
+      <c r="KV24" s="2"/>
+      <c r="KW24" s="2"/>
+      <c r="KX24" s="2"/>
+      <c r="KY24" s="2"/>
+      <c r="KZ24" s="2"/>
+      <c r="LA24" s="2"/>
+      <c r="LB24" s="2"/>
+      <c r="LC24" s="2"/>
+      <c r="LD24" s="2"/>
+      <c r="LE24" s="2"/>
+      <c r="LF24" s="2"/>
+      <c r="LG24" s="2"/>
+      <c r="LH24" s="2"/>
+      <c r="LI24" s="2"/>
+      <c r="LJ24" s="2"/>
+      <c r="LK24" s="2"/>
+      <c r="LL24" s="2"/>
+      <c r="LM24" s="2"/>
+      <c r="LN24" s="2"/>
+      <c r="LO24" s="2"/>
+      <c r="LP24" s="2"/>
+      <c r="LQ24" s="2"/>
+      <c r="LR24" s="2"/>
+      <c r="LS24" s="2"/>
+      <c r="LT24" s="2"/>
+      <c r="LU24" s="2"/>
+      <c r="LV24" s="2"/>
+      <c r="LW24" s="2"/>
+      <c r="LX24" s="2"/>
+      <c r="LY24" s="2"/>
+      <c r="LZ24" s="2"/>
+      <c r="MA24" s="2"/>
+      <c r="MB24" s="2"/>
+      <c r="MC24" s="2"/>
+      <c r="MD24" s="2"/>
+      <c r="ME24" s="2"/>
+      <c r="MF24" s="2"/>
+      <c r="MG24" s="2"/>
+      <c r="MH24" s="2"/>
+      <c r="MI24" s="2"/>
+      <c r="MJ24" s="2"/>
+      <c r="MK24" s="2"/>
+      <c r="ML24" s="2"/>
+      <c r="MM24" s="2"/>
+      <c r="MN24" s="2"/>
+      <c r="MO24" s="2"/>
+      <c r="MP24" s="2"/>
+      <c r="MQ24" s="2"/>
+      <c r="MR24" s="2"/>
+      <c r="MS24" s="2"/>
+      <c r="MT24" s="2"/>
+      <c r="MU24" s="2"/>
+      <c r="MV24" s="2"/>
+      <c r="MW24" s="2"/>
+      <c r="MX24" s="2"/>
+      <c r="MY24" s="2"/>
+      <c r="MZ24" s="2"/>
+      <c r="NA24" s="2"/>
+      <c r="NB24" s="2"/>
+      <c r="NC24" s="2"/>
+      <c r="ND24" s="2"/>
+      <c r="NE24" s="2"/>
+      <c r="NF24" s="2"/>
+      <c r="NG24" s="2"/>
+      <c r="NH24" s="2"/>
+      <c r="NI24" s="2"/>
+      <c r="NJ24" s="2"/>
+      <c r="NK24" s="2"/>
+      <c r="NL24" s="2"/>
+      <c r="NM24" s="2"/>
+      <c r="NN24" s="2"/>
+      <c r="NO24" s="2"/>
+      <c r="NP24" s="2"/>
+      <c r="NQ24" s="2"/>
+      <c r="NR24" s="2"/>
+      <c r="NS24" s="2"/>
+      <c r="NT24" s="2"/>
+      <c r="NU24" s="2"/>
+      <c r="NV24" s="2"/>
+      <c r="NW24" s="2"/>
+      <c r="NX24" s="2"/>
+      <c r="NY24" s="2"/>
+      <c r="NZ24" s="2"/>
+      <c r="OA24" s="2"/>
+      <c r="OB24" s="2"/>
+      <c r="OC24" s="2"/>
+      <c r="OD24" s="2"/>
+      <c r="OE24" s="2"/>
+      <c r="OF24" s="2"/>
+      <c r="OG24" s="2"/>
+      <c r="OH24" s="2"/>
+      <c r="OI24" s="2"/>
+      <c r="OJ24" s="2"/>
+      <c r="OK24" s="2"/>
+      <c r="OL24" s="2"/>
+      <c r="OM24" s="2"/>
+      <c r="ON24" s="2"/>
+      <c r="OO24" s="2"/>
+      <c r="OP24" s="2"/>
+      <c r="OQ24" s="2"/>
+      <c r="OR24" s="2"/>
+      <c r="OS24" s="2"/>
+      <c r="OT24" s="2"/>
+      <c r="OU24" s="2"/>
+      <c r="OV24" s="2"/>
+      <c r="OW24" s="2"/>
+      <c r="OX24" s="2"/>
+      <c r="OY24" s="2"/>
+      <c r="OZ24" s="2"/>
+      <c r="PA24" s="2"/>
+      <c r="PB24" s="2"/>
+      <c r="PC24" s="2"/>
+      <c r="PD24" s="2"/>
+      <c r="PE24" s="2"/>
+      <c r="PF24" s="2"/>
+      <c r="PG24" s="2"/>
+      <c r="PH24" s="2"/>
+      <c r="PI24" s="2"/>
+      <c r="PJ24" s="2"/>
+      <c r="PK24" s="2"/>
+      <c r="PL24" s="2"/>
+      <c r="PM24" s="2"/>
+      <c r="PN24" s="2"/>
+      <c r="PO24" s="2"/>
+      <c r="PP24" s="2"/>
+      <c r="PQ24" s="2"/>
+      <c r="PR24" s="2"/>
+      <c r="PS24" s="2"/>
+      <c r="PT24" s="2"/>
+      <c r="PU24" s="2"/>
+      <c r="PV24" s="2"/>
+      <c r="PW24" s="2"/>
+      <c r="PX24" s="2"/>
+      <c r="PY24" s="2"/>
+      <c r="PZ24" s="2"/>
+      <c r="QA24" s="2"/>
+      <c r="QB24" s="2"/>
+      <c r="QC24" s="2"/>
+      <c r="QD24" s="2"/>
+      <c r="QE24" s="2"/>
+      <c r="QF24" s="2"/>
+      <c r="QG24" s="2"/>
+      <c r="QH24" s="2"/>
+      <c r="QI24" s="2"/>
+      <c r="QJ24" s="2"/>
+      <c r="QK24" s="2"/>
+      <c r="QL24" s="2"/>
+      <c r="QM24" s="2"/>
+      <c r="QN24" s="2"/>
+      <c r="QO24" s="2"/>
+      <c r="QP24" s="2"/>
+      <c r="QQ24" s="2"/>
+      <c r="QR24" s="2"/>
+      <c r="QS24" s="2"/>
+      <c r="QT24" s="2"/>
+      <c r="QU24" s="2"/>
+      <c r="QV24" s="2"/>
+      <c r="QW24" s="2"/>
+      <c r="QX24" s="2"/>
+      <c r="QY24" s="2"/>
+      <c r="QZ24" s="2"/>
+      <c r="RA24" s="2"/>
+      <c r="RB24" s="2"/>
+      <c r="RC24" s="2"/>
+      <c r="RD24" s="2"/>
+      <c r="RE24" s="2"/>
+      <c r="RF24" s="2"/>
+      <c r="RG24" s="2"/>
+      <c r="RH24" s="2"/>
+      <c r="RI24" s="2"/>
+      <c r="RJ24" s="2"/>
+      <c r="RK24" s="2"/>
+      <c r="RL24" s="2"/>
+      <c r="RM24" s="2"/>
+      <c r="RN24" s="2"/>
+      <c r="RO24" s="2"/>
+      <c r="RP24" s="2"/>
+      <c r="RQ24" s="2"/>
+      <c r="RR24" s="2"/>
+      <c r="RS24" s="2"/>
+      <c r="RT24" s="2"/>
+      <c r="RU24" s="2"/>
+      <c r="RV24" s="2"/>
+      <c r="RW24" s="2"/>
+      <c r="RX24" s="2"/>
+      <c r="RY24" s="2"/>
+      <c r="RZ24" s="2"/>
+      <c r="SA24" s="2"/>
+      <c r="SB24" s="2"/>
+      <c r="SC24" s="2"/>
+      <c r="SD24" s="2"/>
+      <c r="SE24" s="2"/>
+      <c r="SF24" s="2"/>
+      <c r="SG24" s="2"/>
+      <c r="SH24" s="2"/>
+      <c r="SI24" s="2"/>
+      <c r="SJ24" s="2"/>
+      <c r="SK24" s="2"/>
+      <c r="SL24" s="2"/>
+      <c r="SM24" s="2"/>
+      <c r="SN24" s="2"/>
+      <c r="SO24" s="2"/>
+      <c r="SP24" s="2"/>
+      <c r="SQ24" s="2"/>
+      <c r="SR24" s="2"/>
+      <c r="SS24" s="2"/>
+      <c r="ST24" s="2"/>
+      <c r="SU24" s="2"/>
+      <c r="SV24" s="2"/>
+      <c r="SW24" s="2"/>
+      <c r="SX24" s="2"/>
+      <c r="SY24" s="2"/>
+      <c r="SZ24" s="2"/>
+      <c r="TA24" s="2"/>
+      <c r="TB24" s="2"/>
+      <c r="TC24" s="2"/>
+      <c r="TD24" s="2"/>
+      <c r="TE24" s="2"/>
+      <c r="TF24" s="2"/>
+      <c r="TG24" s="2"/>
+      <c r="TH24" s="2"/>
+      <c r="TI24" s="2"/>
+      <c r="TJ24" s="2"/>
+      <c r="TK24" s="2"/>
+      <c r="TL24" s="2"/>
+      <c r="TM24" s="2"/>
+      <c r="TN24" s="2"/>
+      <c r="TO24" s="2"/>
+      <c r="TP24" s="2"/>
+      <c r="TQ24" s="2"/>
+      <c r="TR24" s="2"/>
+      <c r="TS24" s="2"/>
+      <c r="TT24" s="2"/>
+      <c r="TU24" s="2"/>
+      <c r="TV24" s="2"/>
+      <c r="TW24" s="2"/>
+      <c r="TX24" s="2"/>
+      <c r="TY24" s="2"/>
+      <c r="TZ24" s="2"/>
+      <c r="UA24" s="2"/>
+      <c r="UB24" s="2"/>
+      <c r="UC24" s="2"/>
+      <c r="UD24" s="2"/>
+      <c r="UE24" s="2"/>
+      <c r="UF24" s="2"/>
+      <c r="UG24" s="2"/>
+      <c r="UH24" s="2"/>
+      <c r="UI24" s="2"/>
+      <c r="UJ24" s="2"/>
+      <c r="UK24" s="2"/>
+      <c r="UL24" s="2"/>
+      <c r="UM24" s="2"/>
+      <c r="UN24" s="2"/>
+      <c r="UO24" s="2"/>
+      <c r="UP24" s="2"/>
+      <c r="UQ24" s="2"/>
+      <c r="UR24" s="2"/>
+      <c r="US24" s="2"/>
+      <c r="UT24" s="2"/>
+      <c r="UU24" s="2"/>
+      <c r="UV24" s="2"/>
+      <c r="UW24" s="2"/>
+      <c r="UX24" s="2"/>
+      <c r="UY24" s="2"/>
+      <c r="UZ24" s="2"/>
+      <c r="VA24" s="2"/>
+      <c r="VB24" s="2"/>
+      <c r="VC24" s="2"/>
+      <c r="VD24" s="2"/>
+      <c r="VE24" s="2"/>
+      <c r="VF24" s="2"/>
+      <c r="VG24" s="2"/>
+      <c r="VH24" s="2"/>
+      <c r="VI24" s="2"/>
+      <c r="VJ24" s="2"/>
+      <c r="VK24" s="2"/>
+      <c r="VL24" s="2"/>
+      <c r="VM24" s="2"/>
+      <c r="VN24" s="2"/>
+      <c r="VO24" s="2"/>
+      <c r="VP24" s="2"/>
+      <c r="VQ24" s="2"/>
+      <c r="VR24" s="2"/>
+      <c r="VS24" s="2"/>
+      <c r="VT24" s="2"/>
+      <c r="VU24" s="2"/>
+      <c r="VV24" s="2"/>
+      <c r="VW24" s="2"/>
+      <c r="VX24" s="2"/>
+      <c r="VY24" s="2"/>
+      <c r="VZ24" s="2"/>
+      <c r="WA24" s="2"/>
+      <c r="WB24" s="2"/>
+      <c r="WC24" s="2"/>
+      <c r="WD24" s="2"/>
+      <c r="WE24" s="2"/>
+      <c r="WF24" s="2"/>
+      <c r="WG24" s="2"/>
+      <c r="WH24" s="2"/>
+      <c r="WI24" s="2"/>
+      <c r="WJ24" s="2"/>
+      <c r="WK24" s="2"/>
+      <c r="WL24" s="2"/>
+      <c r="WM24" s="2"/>
+      <c r="WN24" s="2"/>
+      <c r="WO24" s="2"/>
+      <c r="WP24" s="2"/>
+      <c r="WQ24" s="2"/>
+      <c r="WR24" s="2"/>
+      <c r="WS24" s="2"/>
+      <c r="WT24" s="2"/>
+      <c r="WU24" s="2"/>
+      <c r="WV24" s="2"/>
+      <c r="WW24" s="2"/>
+      <c r="WX24" s="2"/>
+      <c r="WY24" s="2"/>
+      <c r="WZ24" s="2"/>
+      <c r="XA24" s="2"/>
+      <c r="XB24" s="2"/>
+      <c r="XC24" s="2"/>
+      <c r="XD24" s="2"/>
+      <c r="XE24" s="2"/>
+      <c r="XF24" s="2"/>
+      <c r="XG24" s="2"/>
+      <c r="XH24" s="2"/>
+      <c r="XI24" s="2"/>
+      <c r="XJ24" s="2"/>
+      <c r="XK24" s="2"/>
+      <c r="XL24" s="2"/>
+      <c r="XM24" s="2"/>
+      <c r="XN24" s="2"/>
+      <c r="XO24" s="2"/>
+      <c r="XP24" s="2"/>
+      <c r="XQ24" s="2"/>
+      <c r="XR24" s="2"/>
+      <c r="XS24" s="2"/>
+      <c r="XT24" s="2"/>
+      <c r="XU24" s="2"/>
+      <c r="XV24" s="2"/>
+      <c r="XW24" s="2"/>
+      <c r="XX24" s="2"/>
+      <c r="XY24" s="2"/>
+      <c r="XZ24" s="2"/>
+      <c r="YA24" s="2"/>
+      <c r="YB24" s="2"/>
+      <c r="YC24" s="2"/>
+      <c r="YD24" s="2"/>
+      <c r="YE24" s="2"/>
+      <c r="YF24" s="2"/>
+      <c r="YG24" s="2"/>
+      <c r="YH24" s="2"/>
+      <c r="YI24" s="2"/>
+      <c r="YJ24" s="2"/>
+      <c r="YK24" s="2"/>
+      <c r="YL24" s="2"/>
+      <c r="YM24" s="2"/>
+      <c r="YN24" s="2"/>
+      <c r="YO24" s="2"/>
+      <c r="YP24" s="2"/>
+      <c r="YQ24" s="2"/>
+      <c r="YR24" s="2"/>
+      <c r="YS24" s="2"/>
+      <c r="YT24" s="2"/>
+      <c r="YU24" s="2"/>
+      <c r="YV24" s="2"/>
+      <c r="YW24" s="2"/>
+      <c r="YX24" s="2"/>
+      <c r="YY24" s="2"/>
+      <c r="YZ24" s="2"/>
+      <c r="ZA24" s="2"/>
+      <c r="ZB24" s="2"/>
+      <c r="ZC24" s="2"/>
+      <c r="ZD24" s="2"/>
+      <c r="ZE24" s="2"/>
+      <c r="ZF24" s="2"/>
+      <c r="ZG24" s="2"/>
+      <c r="ZH24" s="2"/>
+      <c r="ZI24" s="2"/>
+      <c r="ZJ24" s="2"/>
+      <c r="ZK24" s="2"/>
+      <c r="ZL24" s="2"/>
+      <c r="ZM24" s="2"/>
+      <c r="ZN24" s="2"/>
+      <c r="ZO24" s="2"/>
+      <c r="ZP24" s="2"/>
+      <c r="ZQ24" s="2"/>
+      <c r="ZR24" s="2"/>
+      <c r="ZS24" s="2"/>
+      <c r="ZT24" s="2"/>
+      <c r="ZU24" s="2"/>
+      <c r="ZV24" s="2"/>
+      <c r="ZW24" s="2"/>
+      <c r="ZX24" s="2"/>
+      <c r="ZY24" s="2"/>
+      <c r="ZZ24" s="2"/>
+      <c r="AAA24" s="2"/>
+      <c r="AAB24" s="2"/>
+      <c r="AAC24" s="2"/>
+      <c r="AAD24" s="2"/>
+      <c r="AAE24" s="2"/>
+      <c r="AAF24" s="2"/>
+      <c r="AAG24" s="2"/>
+      <c r="AAH24" s="2"/>
+      <c r="AAI24" s="2"/>
+      <c r="AAJ24" s="2"/>
+      <c r="AAK24" s="2"/>
+      <c r="AAL24" s="2"/>
+      <c r="AAM24" s="2"/>
+      <c r="AAN24" s="2"/>
+      <c r="AAO24" s="2"/>
+      <c r="AAP24" s="2"/>
+      <c r="AAQ24" s="2"/>
+      <c r="AAR24" s="2"/>
+      <c r="AAS24" s="2"/>
+      <c r="AAT24" s="2"/>
+      <c r="AAU24" s="2"/>
+      <c r="AAV24" s="2"/>
+      <c r="AAW24" s="2"/>
+      <c r="AAX24" s="2"/>
+      <c r="AAY24" s="2"/>
+      <c r="AAZ24" s="2"/>
+      <c r="ABA24" s="2"/>
+      <c r="ABB24" s="2"/>
+      <c r="ABC24" s="2"/>
+      <c r="ABD24" s="2"/>
+      <c r="ABE24" s="2"/>
+      <c r="ABF24" s="2"/>
+      <c r="ABG24" s="2"/>
+      <c r="ABH24" s="2"/>
+      <c r="ABI24" s="2"/>
+      <c r="ABJ24" s="2"/>
+      <c r="ABK24" s="2"/>
+      <c r="ABL24" s="2"/>
+      <c r="ABM24" s="2"/>
+      <c r="ABN24" s="2"/>
+      <c r="ABO24" s="2"/>
+      <c r="ABP24" s="2"/>
+      <c r="ABQ24" s="2"/>
+      <c r="ABR24" s="2"/>
+      <c r="ABS24" s="2"/>
+      <c r="ABT24" s="2"/>
+      <c r="ABU24" s="2"/>
+      <c r="ABV24" s="2"/>
+      <c r="ABW24" s="2"/>
+      <c r="ABX24" s="2"/>
+      <c r="ABY24" s="2"/>
+      <c r="ABZ24" s="2"/>
+      <c r="ACA24" s="2"/>
+      <c r="ACB24" s="2"/>
+      <c r="ACC24" s="2"/>
+      <c r="ACD24" s="2"/>
+      <c r="ACE24" s="2"/>
+      <c r="ACF24" s="2"/>
+      <c r="ACG24" s="2"/>
+      <c r="ACH24" s="2"/>
+      <c r="ACI24" s="2"/>
+      <c r="ACJ24" s="2"/>
+      <c r="ACK24" s="2"/>
+      <c r="ACL24" s="2"/>
+      <c r="ACM24" s="2"/>
+      <c r="ACN24" s="2"/>
+      <c r="ACO24" s="2"/>
+      <c r="ACP24" s="2"/>
+      <c r="ACQ24" s="2"/>
+      <c r="ACR24" s="2"/>
+      <c r="ACS24" s="2"/>
+      <c r="ACT24" s="2"/>
+      <c r="ACU24" s="2"/>
+      <c r="ACV24" s="2"/>
+      <c r="ACW24" s="2"/>
+      <c r="ACX24" s="2"/>
+      <c r="ACY24" s="2"/>
+      <c r="ACZ24" s="2"/>
+      <c r="ADA24" s="2"/>
+      <c r="ADB24" s="2"/>
+      <c r="ADC24" s="2"/>
+      <c r="ADD24" s="2"/>
+      <c r="ADE24" s="2"/>
+      <c r="ADF24" s="2"/>
+      <c r="ADG24" s="2"/>
+      <c r="ADH24" s="2"/>
+      <c r="ADI24" s="2"/>
+      <c r="ADJ24" s="2"/>
+      <c r="ADK24" s="2"/>
+      <c r="ADL24" s="2"/>
+      <c r="ADM24" s="2"/>
+      <c r="ADN24" s="2"/>
+      <c r="ADO24" s="2"/>
+      <c r="ADP24" s="2"/>
+      <c r="ADQ24" s="2"/>
+      <c r="ADR24" s="2"/>
+      <c r="ADS24" s="2"/>
+      <c r="ADT24" s="2"/>
+      <c r="ADU24" s="2"/>
+      <c r="ADV24" s="2"/>
+      <c r="ADW24" s="2"/>
+      <c r="ADX24" s="2"/>
+      <c r="ADY24" s="2"/>
+      <c r="ADZ24" s="2"/>
+      <c r="AEA24" s="2"/>
+      <c r="AEB24" s="2"/>
+      <c r="AEC24" s="2"/>
+      <c r="AED24" s="2"/>
+      <c r="AEE24" s="2"/>
+      <c r="AEF24" s="2"/>
+      <c r="AEG24" s="2"/>
+      <c r="AEH24" s="2"/>
+      <c r="AEI24" s="2"/>
+      <c r="AEJ24" s="2"/>
+      <c r="AEK24" s="2"/>
+      <c r="AEL24" s="2"/>
+      <c r="AEM24" s="2"/>
+      <c r="AEN24" s="2"/>
+      <c r="AEO24" s="2"/>
+      <c r="AEP24" s="2"/>
+      <c r="AEQ24" s="2"/>
+      <c r="AER24" s="2"/>
+      <c r="AES24" s="2"/>
+      <c r="AET24" s="2"/>
+      <c r="AEU24" s="2"/>
+      <c r="AEV24" s="2"/>
+      <c r="AEW24" s="2"/>
+      <c r="AEX24" s="2"/>
+      <c r="AEY24" s="2"/>
+      <c r="AEZ24" s="2"/>
+      <c r="AFA24" s="2"/>
+      <c r="AFB24" s="2"/>
+      <c r="AFC24" s="2"/>
+      <c r="AFD24" s="2"/>
+      <c r="AFE24" s="2"/>
+      <c r="AFF24" s="2"/>
+      <c r="AFG24" s="2"/>
+      <c r="AFH24" s="2"/>
+      <c r="AFI24" s="2"/>
+      <c r="AFJ24" s="2"/>
+      <c r="AFK24" s="2"/>
+      <c r="AFL24" s="2"/>
+      <c r="AFM24" s="2"/>
+      <c r="AFN24" s="2"/>
+      <c r="AFO24" s="2"/>
+      <c r="AFP24" s="2"/>
+      <c r="AFQ24" s="2"/>
+      <c r="AFR24" s="2"/>
+      <c r="AFS24" s="2"/>
+      <c r="AFT24" s="2"/>
+      <c r="AFU24" s="2"/>
+      <c r="AFV24" s="2"/>
+      <c r="AFW24" s="2"/>
+      <c r="AFX24" s="2"/>
+      <c r="AFY24" s="2"/>
+      <c r="AFZ24" s="2"/>
+      <c r="AGA24" s="2"/>
+      <c r="AGB24" s="2"/>
+      <c r="AGC24" s="2"/>
+      <c r="AGD24" s="2"/>
+      <c r="AGE24" s="2"/>
+      <c r="AGF24" s="2"/>
+      <c r="AGG24" s="2"/>
+      <c r="AGH24" s="2"/>
+      <c r="AGI24" s="2"/>
+      <c r="AGJ24" s="2"/>
+      <c r="AGK24" s="2"/>
+      <c r="AGL24" s="2"/>
+      <c r="AGM24" s="2"/>
+      <c r="AGN24" s="2"/>
+      <c r="AGO24" s="2"/>
+      <c r="AGP24" s="2"/>
+      <c r="AGQ24" s="2"/>
+      <c r="AGR24" s="2"/>
+      <c r="AGS24" s="2"/>
+      <c r="AGT24" s="2"/>
+      <c r="AGU24" s="2"/>
+      <c r="AGV24" s="2"/>
+      <c r="AGW24" s="2"/>
+      <c r="AGX24" s="2"/>
+      <c r="AGY24" s="2"/>
+      <c r="AGZ24" s="2"/>
+      <c r="AHA24" s="2"/>
+      <c r="AHB24" s="2"/>
+      <c r="AHC24" s="2"/>
+      <c r="AHD24" s="2"/>
+      <c r="AHE24" s="2"/>
+      <c r="AHF24" s="2"/>
+      <c r="AHG24" s="2"/>
+      <c r="AHH24" s="2"/>
+      <c r="AHI24" s="2"/>
+      <c r="AHJ24" s="2"/>
+      <c r="AHK24" s="2"/>
+      <c r="AHL24" s="2"/>
+      <c r="AHM24" s="2"/>
+      <c r="AHN24" s="2"/>
+      <c r="AHO24" s="2"/>
+      <c r="AHP24" s="2"/>
+      <c r="AHQ24" s="2"/>
+      <c r="AHR24" s="2"/>
+      <c r="AHS24" s="2"/>
+      <c r="AHT24" s="2"/>
+      <c r="AHU24" s="2"/>
+      <c r="AHV24" s="2"/>
+      <c r="AHW24" s="2"/>
+      <c r="AHX24" s="2"/>
+      <c r="AHY24" s="2"/>
+      <c r="AHZ24" s="2"/>
+      <c r="AIA24" s="2"/>
+      <c r="AIB24" s="2"/>
+      <c r="AIC24" s="2"/>
+      <c r="AID24" s="2"/>
+      <c r="AIE24" s="2"/>
+      <c r="AIF24" s="2"/>
+      <c r="AIG24" s="2"/>
+      <c r="AIH24" s="2"/>
+      <c r="AII24" s="2"/>
+      <c r="AIJ24" s="2"/>
+      <c r="AIK24" s="2"/>
+      <c r="AIL24" s="2"/>
+      <c r="AIM24" s="2"/>
+      <c r="AIN24" s="2"/>
+      <c r="AIO24" s="2"/>
+      <c r="AIP24" s="2"/>
+      <c r="AIQ24" s="2"/>
+      <c r="AIR24" s="2"/>
+      <c r="AIS24" s="2"/>
+      <c r="AIT24" s="2"/>
+      <c r="AIU24" s="2"/>
+      <c r="AIV24" s="2"/>
+      <c r="AIW24" s="2"/>
+      <c r="AIX24" s="2"/>
+      <c r="AIY24" s="2"/>
+      <c r="AIZ24" s="2"/>
+      <c r="AJA24" s="2"/>
+      <c r="AJB24" s="2"/>
+      <c r="AJC24" s="2"/>
+      <c r="AJD24" s="2"/>
+      <c r="AJE24" s="2"/>
+      <c r="AJF24" s="2"/>
+      <c r="AJG24" s="2"/>
+      <c r="AJH24" s="2"/>
+      <c r="AJI24" s="2"/>
+      <c r="AJJ24" s="2"/>
+      <c r="AJK24" s="2"/>
+      <c r="AJL24" s="2"/>
+      <c r="AJM24" s="2"/>
+      <c r="AJN24" s="2"/>
+      <c r="AJO24" s="2"/>
+      <c r="AJP24" s="2"/>
+      <c r="AJQ24" s="2"/>
+      <c r="AJR24" s="2"/>
+      <c r="AJS24" s="2"/>
+      <c r="AJT24" s="2"/>
+      <c r="AJU24" s="2"/>
+      <c r="AJV24" s="2"/>
+      <c r="AJW24" s="2"/>
+      <c r="AJX24" s="2"/>
+      <c r="AJY24" s="2"/>
+      <c r="AJZ24" s="2"/>
+      <c r="AKA24" s="2"/>
+      <c r="AKB24" s="2"/>
+      <c r="AKC24" s="2"/>
+      <c r="AKD24" s="2"/>
+      <c r="AKE24" s="2"/>
+      <c r="AKF24" s="2"/>
+      <c r="AKG24" s="2"/>
+      <c r="AKH24" s="2"/>
+      <c r="AKI24" s="2"/>
+      <c r="AKJ24" s="2"/>
+      <c r="AKK24" s="2"/>
+      <c r="AKL24" s="2"/>
+      <c r="AKM24" s="2"/>
+      <c r="AKN24" s="2"/>
+      <c r="AKO24" s="2"/>
+      <c r="AKP24" s="2"/>
+      <c r="AKQ24" s="2"/>
+      <c r="AKR24" s="2"/>
+      <c r="AKS24" s="2"/>
+      <c r="AKT24" s="2"/>
+      <c r="AKU24" s="2"/>
+      <c r="AKV24" s="2"/>
+      <c r="AKW24" s="2"/>
+      <c r="AKX24" s="2"/>
+      <c r="AKY24" s="2"/>
+      <c r="AKZ24" s="2"/>
+      <c r="ALA24" s="2"/>
+      <c r="ALB24" s="2"/>
+      <c r="ALC24" s="2"/>
+      <c r="ALD24" s="2"/>
+      <c r="ALE24" s="2"/>
+      <c r="ALF24" s="2"/>
+      <c r="ALG24" s="2"/>
+      <c r="ALH24" s="2"/>
+      <c r="ALI24" s="2"/>
+      <c r="ALJ24" s="2"/>
+      <c r="ALK24" s="2"/>
+      <c r="ALL24" s="2"/>
+      <c r="ALM24" s="2"/>
+      <c r="ALN24" s="2"/>
+      <c r="ALO24" s="2"/>
+      <c r="ALP24" s="2"/>
+      <c r="ALQ24" s="2"/>
+      <c r="ALR24" s="2"/>
+      <c r="ALS24" s="2"/>
+      <c r="ALT24" s="2"/>
+      <c r="ALU24" s="2"/>
+      <c r="ALV24" s="2"/>
+      <c r="ALW24" s="2"/>
+      <c r="ALX24" s="2"/>
+      <c r="ALY24" s="2"/>
+      <c r="ALZ24" s="2"/>
+      <c r="AMA24" s="2"/>
+      <c r="AMB24" s="2"/>
+      <c r="AMC24" s="2"/>
+      <c r="AMD24" s="2"/>
+      <c r="AME24" s="2"/>
+      <c r="AMF24" s="2"/>
+      <c r="AMG24" s="2"/>
+      <c r="AMH24" s="2"/>
+      <c r="AMI24" s="2"/>
+      <c r="AMJ24" s="2"/>
+      <c r="AMK24" s="2"/>
+    </row>
+    <row r="25" spans="1:1025" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
+      <c r="Z25" s="2"/>
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="2"/>
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="2"/>
+      <c r="AE25" s="2"/>
+      <c r="AF25" s="2"/>
+      <c r="AG25" s="2"/>
+      <c r="AH25" s="2"/>
+      <c r="AI25" s="2"/>
+      <c r="AJ25" s="2"/>
+      <c r="AK25" s="2"/>
+      <c r="AL25" s="2"/>
+      <c r="AM25" s="2"/>
+      <c r="AN25" s="2"/>
+      <c r="AO25" s="2"/>
+      <c r="AP25" s="2"/>
+      <c r="AQ25" s="2"/>
+      <c r="AR25" s="2"/>
+      <c r="AS25" s="2"/>
+      <c r="AT25" s="2"/>
+      <c r="AU25" s="2"/>
+      <c r="AV25" s="2"/>
+      <c r="AW25" s="2"/>
+      <c r="AX25" s="2"/>
+      <c r="AY25" s="2"/>
+      <c r="AZ25" s="2"/>
+      <c r="BA25" s="2"/>
+      <c r="BB25" s="2"/>
+      <c r="BC25" s="2"/>
+      <c r="BD25" s="2"/>
+      <c r="BE25" s="2"/>
+      <c r="BF25" s="2"/>
+      <c r="BG25" s="2"/>
+      <c r="BH25" s="2"/>
+      <c r="BI25" s="2"/>
+      <c r="BJ25" s="2"/>
+      <c r="BK25" s="2"/>
+      <c r="BL25" s="2"/>
+      <c r="BM25" s="2"/>
+      <c r="BN25" s="2"/>
+      <c r="BO25" s="2"/>
+      <c r="BP25" s="2"/>
+      <c r="BQ25" s="2"/>
+      <c r="BR25" s="2"/>
+      <c r="BS25" s="2"/>
+      <c r="BT25" s="2"/>
+      <c r="BU25" s="2"/>
+      <c r="BV25" s="2"/>
+      <c r="BW25" s="2"/>
+      <c r="BX25" s="2"/>
+      <c r="BY25" s="2"/>
+      <c r="BZ25" s="2"/>
+      <c r="CA25" s="2"/>
+      <c r="CB25" s="2"/>
+      <c r="CC25" s="2"/>
+      <c r="CD25" s="2"/>
+      <c r="CE25" s="2"/>
+      <c r="CF25" s="2"/>
+      <c r="CG25" s="2"/>
+      <c r="CH25" s="2"/>
+      <c r="CI25" s="2"/>
+      <c r="CJ25" s="2"/>
+      <c r="CK25" s="2"/>
+      <c r="CL25" s="2"/>
+      <c r="CM25" s="2"/>
+      <c r="CN25" s="2"/>
+      <c r="CO25" s="2"/>
+      <c r="CP25" s="2"/>
+      <c r="CQ25" s="2"/>
+      <c r="CR25" s="2"/>
+      <c r="CS25" s="2"/>
+      <c r="CT25" s="2"/>
+      <c r="CU25" s="2"/>
+      <c r="CV25" s="2"/>
+      <c r="CW25" s="2"/>
+      <c r="CX25" s="2"/>
+      <c r="CY25" s="2"/>
+      <c r="CZ25" s="2"/>
+      <c r="DA25" s="2"/>
+      <c r="DB25" s="2"/>
+      <c r="DC25" s="2"/>
+      <c r="DD25" s="2"/>
+      <c r="DE25" s="2"/>
+      <c r="DF25" s="2"/>
+      <c r="DG25" s="2"/>
+      <c r="DH25" s="2"/>
+      <c r="DI25" s="2"/>
+      <c r="DJ25" s="2"/>
+      <c r="DK25" s="2"/>
+      <c r="DL25" s="2"/>
+      <c r="DM25" s="2"/>
+      <c r="DN25" s="2"/>
+      <c r="DO25" s="2"/>
+      <c r="DP25" s="2"/>
+      <c r="DQ25" s="2"/>
+      <c r="DR25" s="2"/>
+      <c r="DS25" s="2"/>
+      <c r="DT25" s="2"/>
+      <c r="DU25" s="2"/>
+      <c r="DV25" s="2"/>
+      <c r="DW25" s="2"/>
+      <c r="DX25" s="2"/>
+      <c r="DY25" s="2"/>
+      <c r="DZ25" s="2"/>
+      <c r="EA25" s="2"/>
+      <c r="EB25" s="2"/>
+      <c r="EC25" s="2"/>
+      <c r="ED25" s="2"/>
+      <c r="EE25" s="2"/>
+      <c r="EF25" s="2"/>
+      <c r="EG25" s="2"/>
+      <c r="EH25" s="2"/>
+      <c r="EI25" s="2"/>
+      <c r="EJ25" s="2"/>
+      <c r="EK25" s="2"/>
+      <c r="EL25" s="2"/>
+      <c r="EM25" s="2"/>
+      <c r="EN25" s="2"/>
+      <c r="EO25" s="2"/>
+      <c r="EP25" s="2"/>
+      <c r="EQ25" s="2"/>
+      <c r="ER25" s="2"/>
+      <c r="ES25" s="2"/>
+      <c r="ET25" s="2"/>
+      <c r="EU25" s="2"/>
+      <c r="EV25" s="2"/>
+      <c r="EW25" s="2"/>
+      <c r="EX25" s="2"/>
+      <c r="EY25" s="2"/>
+      <c r="EZ25" s="2"/>
+      <c r="FA25" s="2"/>
+      <c r="FB25" s="2"/>
+      <c r="FC25" s="2"/>
+      <c r="FD25" s="2"/>
+      <c r="FE25" s="2"/>
+      <c r="FF25" s="2"/>
+      <c r="FG25" s="2"/>
+      <c r="FH25" s="2"/>
+      <c r="FI25" s="2"/>
+      <c r="FJ25" s="2"/>
+      <c r="FK25" s="2"/>
+      <c r="FL25" s="2"/>
+      <c r="FM25" s="2"/>
+      <c r="FN25" s="2"/>
+      <c r="FO25" s="2"/>
+      <c r="FP25" s="2"/>
+      <c r="FQ25" s="2"/>
+      <c r="FR25" s="2"/>
+      <c r="FS25" s="2"/>
+      <c r="FT25" s="2"/>
+      <c r="FU25" s="2"/>
+      <c r="FV25" s="2"/>
+      <c r="FW25" s="2"/>
+      <c r="FX25" s="2"/>
+      <c r="FY25" s="2"/>
+      <c r="FZ25" s="2"/>
+      <c r="GA25" s="2"/>
+      <c r="GB25" s="2"/>
+      <c r="GC25" s="2"/>
+      <c r="GD25" s="2"/>
+      <c r="GE25" s="2"/>
+      <c r="GF25" s="2"/>
+      <c r="GG25" s="2"/>
+      <c r="GH25" s="2"/>
+      <c r="GI25" s="2"/>
+      <c r="GJ25" s="2"/>
+      <c r="GK25" s="2"/>
+      <c r="GL25" s="2"/>
+      <c r="GM25" s="2"/>
+      <c r="GN25" s="2"/>
+      <c r="GO25" s="2"/>
+      <c r="GP25" s="2"/>
+      <c r="GQ25" s="2"/>
+      <c r="GR25" s="2"/>
+      <c r="GS25" s="2"/>
+      <c r="GT25" s="2"/>
+      <c r="GU25" s="2"/>
+      <c r="GV25" s="2"/>
+      <c r="GW25" s="2"/>
+      <c r="GX25" s="2"/>
+      <c r="GY25" s="2"/>
+      <c r="GZ25" s="2"/>
+      <c r="HA25" s="2"/>
+      <c r="HB25" s="2"/>
+      <c r="HC25" s="2"/>
+      <c r="HD25" s="2"/>
+      <c r="HE25" s="2"/>
+      <c r="HF25" s="2"/>
+      <c r="HG25" s="2"/>
+      <c r="HH25" s="2"/>
+      <c r="HI25" s="2"/>
+      <c r="HJ25" s="2"/>
+      <c r="HK25" s="2"/>
+      <c r="HL25" s="2"/>
+      <c r="HM25" s="2"/>
+      <c r="HN25" s="2"/>
+      <c r="HO25" s="2"/>
+      <c r="HP25" s="2"/>
+      <c r="HQ25" s="2"/>
+      <c r="HR25" s="2"/>
+      <c r="HS25" s="2"/>
+      <c r="HT25" s="2"/>
+      <c r="HU25" s="2"/>
+      <c r="HV25" s="2"/>
+      <c r="HW25" s="2"/>
+      <c r="HX25" s="2"/>
+      <c r="HY25" s="2"/>
+      <c r="HZ25" s="2"/>
+      <c r="IA25" s="2"/>
+      <c r="IB25" s="2"/>
+      <c r="IC25" s="2"/>
+      <c r="ID25" s="2"/>
+      <c r="IE25" s="2"/>
+      <c r="IF25" s="2"/>
+      <c r="IG25" s="2"/>
+      <c r="IH25" s="2"/>
+      <c r="II25" s="2"/>
+      <c r="IJ25" s="2"/>
+      <c r="IK25" s="2"/>
+      <c r="IL25" s="2"/>
+      <c r="IM25" s="2"/>
+      <c r="IN25" s="2"/>
+      <c r="IO25" s="2"/>
+      <c r="IP25" s="2"/>
+      <c r="IQ25" s="2"/>
+      <c r="IR25" s="2"/>
+      <c r="IS25" s="2"/>
+      <c r="IT25" s="2"/>
+      <c r="IU25" s="2"/>
+      <c r="IV25" s="2"/>
+      <c r="IW25" s="2"/>
+      <c r="IX25" s="2"/>
+      <c r="IY25" s="2"/>
+      <c r="IZ25" s="2"/>
+      <c r="JA25" s="2"/>
+      <c r="JB25" s="2"/>
+      <c r="JC25" s="2"/>
+      <c r="JD25" s="2"/>
+      <c r="JE25" s="2"/>
+      <c r="JF25" s="2"/>
+      <c r="JG25" s="2"/>
+      <c r="JH25" s="2"/>
+      <c r="JI25" s="2"/>
+      <c r="JJ25" s="2"/>
+      <c r="JK25" s="2"/>
+      <c r="JL25" s="2"/>
+      <c r="JM25" s="2"/>
+      <c r="JN25" s="2"/>
+      <c r="JO25" s="2"/>
+      <c r="JP25" s="2"/>
+      <c r="JQ25" s="2"/>
+      <c r="JR25" s="2"/>
+      <c r="JS25" s="2"/>
+      <c r="JT25" s="2"/>
+      <c r="JU25" s="2"/>
+      <c r="JV25" s="2"/>
+      <c r="JW25" s="2"/>
+      <c r="JX25" s="2"/>
+      <c r="JY25" s="2"/>
+      <c r="JZ25" s="2"/>
+      <c r="KA25" s="2"/>
+      <c r="KB25" s="2"/>
+      <c r="KC25" s="2"/>
+      <c r="KD25" s="2"/>
+      <c r="KE25" s="2"/>
+      <c r="KF25" s="2"/>
+      <c r="KG25" s="2"/>
+      <c r="KH25" s="2"/>
+      <c r="KI25" s="2"/>
+      <c r="KJ25" s="2"/>
+      <c r="KK25" s="2"/>
+      <c r="KL25" s="2"/>
+      <c r="KM25" s="2"/>
+      <c r="KN25" s="2"/>
+      <c r="KO25" s="2"/>
+      <c r="KP25" s="2"/>
+      <c r="KQ25" s="2"/>
+      <c r="KR25" s="2"/>
+      <c r="KS25" s="2"/>
+      <c r="KT25" s="2"/>
+      <c r="KU25" s="2"/>
+      <c r="KV25" s="2"/>
+      <c r="KW25" s="2"/>
+      <c r="KX25" s="2"/>
+      <c r="KY25" s="2"/>
+      <c r="KZ25" s="2"/>
+      <c r="LA25" s="2"/>
+      <c r="LB25" s="2"/>
+      <c r="LC25" s="2"/>
+      <c r="LD25" s="2"/>
+      <c r="LE25" s="2"/>
+      <c r="LF25" s="2"/>
+      <c r="LG25" s="2"/>
+      <c r="LH25" s="2"/>
+      <c r="LI25" s="2"/>
+      <c r="LJ25" s="2"/>
+      <c r="LK25" s="2"/>
+      <c r="LL25" s="2"/>
+      <c r="LM25" s="2"/>
+      <c r="LN25" s="2"/>
+      <c r="LO25" s="2"/>
+      <c r="LP25" s="2"/>
+      <c r="LQ25" s="2"/>
+      <c r="LR25" s="2"/>
+      <c r="LS25" s="2"/>
+      <c r="LT25" s="2"/>
+      <c r="LU25" s="2"/>
+      <c r="LV25" s="2"/>
+      <c r="LW25" s="2"/>
+      <c r="LX25" s="2"/>
+      <c r="LY25" s="2"/>
+      <c r="LZ25" s="2"/>
+      <c r="MA25" s="2"/>
+      <c r="MB25" s="2"/>
+      <c r="MC25" s="2"/>
+      <c r="MD25" s="2"/>
+      <c r="ME25" s="2"/>
+      <c r="MF25" s="2"/>
+      <c r="MG25" s="2"/>
+      <c r="MH25" s="2"/>
+      <c r="MI25" s="2"/>
+      <c r="MJ25" s="2"/>
+      <c r="MK25" s="2"/>
+      <c r="ML25" s="2"/>
+      <c r="MM25" s="2"/>
+      <c r="MN25" s="2"/>
+      <c r="MO25" s="2"/>
+      <c r="MP25" s="2"/>
+      <c r="MQ25" s="2"/>
+      <c r="MR25" s="2"/>
+      <c r="MS25" s="2"/>
+      <c r="MT25" s="2"/>
+      <c r="MU25" s="2"/>
+      <c r="MV25" s="2"/>
+      <c r="MW25" s="2"/>
+      <c r="MX25" s="2"/>
+      <c r="MY25" s="2"/>
+      <c r="MZ25" s="2"/>
+      <c r="NA25" s="2"/>
+      <c r="NB25" s="2"/>
+      <c r="NC25" s="2"/>
+      <c r="ND25" s="2"/>
+      <c r="NE25" s="2"/>
+      <c r="NF25" s="2"/>
+      <c r="NG25" s="2"/>
+      <c r="NH25" s="2"/>
+      <c r="NI25" s="2"/>
+      <c r="NJ25" s="2"/>
+      <c r="NK25" s="2"/>
+      <c r="NL25" s="2"/>
+      <c r="NM25" s="2"/>
+      <c r="NN25" s="2"/>
+      <c r="NO25" s="2"/>
+      <c r="NP25" s="2"/>
+      <c r="NQ25" s="2"/>
+      <c r="NR25" s="2"/>
+      <c r="NS25" s="2"/>
+      <c r="NT25" s="2"/>
+      <c r="NU25" s="2"/>
+      <c r="NV25" s="2"/>
+      <c r="NW25" s="2"/>
+      <c r="NX25" s="2"/>
+      <c r="NY25" s="2"/>
+      <c r="NZ25" s="2"/>
+      <c r="OA25" s="2"/>
+      <c r="OB25" s="2"/>
+      <c r="OC25" s="2"/>
+      <c r="OD25" s="2"/>
+      <c r="OE25" s="2"/>
+      <c r="OF25" s="2"/>
+      <c r="OG25" s="2"/>
+      <c r="OH25" s="2"/>
+      <c r="OI25" s="2"/>
+      <c r="OJ25" s="2"/>
+      <c r="OK25" s="2"/>
+      <c r="OL25" s="2"/>
+      <c r="OM25" s="2"/>
+      <c r="ON25" s="2"/>
+      <c r="OO25" s="2"/>
+      <c r="OP25" s="2"/>
+      <c r="OQ25" s="2"/>
+      <c r="OR25" s="2"/>
+      <c r="OS25" s="2"/>
+      <c r="OT25" s="2"/>
+      <c r="OU25" s="2"/>
+      <c r="OV25" s="2"/>
+      <c r="OW25" s="2"/>
+      <c r="OX25" s="2"/>
+      <c r="OY25" s="2"/>
+      <c r="OZ25" s="2"/>
+      <c r="PA25" s="2"/>
+      <c r="PB25" s="2"/>
+      <c r="PC25" s="2"/>
+      <c r="PD25" s="2"/>
+      <c r="PE25" s="2"/>
+      <c r="PF25" s="2"/>
+      <c r="PG25" s="2"/>
+      <c r="PH25" s="2"/>
+      <c r="PI25" s="2"/>
+      <c r="PJ25" s="2"/>
+      <c r="PK25" s="2"/>
+      <c r="PL25" s="2"/>
+      <c r="PM25" s="2"/>
+      <c r="PN25" s="2"/>
+      <c r="PO25" s="2"/>
+      <c r="PP25" s="2"/>
+      <c r="PQ25" s="2"/>
+      <c r="PR25" s="2"/>
+      <c r="PS25" s="2"/>
+      <c r="PT25" s="2"/>
+      <c r="PU25" s="2"/>
+      <c r="PV25" s="2"/>
+      <c r="PW25" s="2"/>
+      <c r="PX25" s="2"/>
+      <c r="PY25" s="2"/>
+      <c r="PZ25" s="2"/>
+      <c r="QA25" s="2"/>
+      <c r="QB25" s="2"/>
+      <c r="QC25" s="2"/>
+      <c r="QD25" s="2"/>
+      <c r="QE25" s="2"/>
+      <c r="QF25" s="2"/>
+      <c r="QG25" s="2"/>
+      <c r="QH25" s="2"/>
+      <c r="QI25" s="2"/>
+      <c r="QJ25" s="2"/>
+      <c r="QK25" s="2"/>
+      <c r="QL25" s="2"/>
+      <c r="QM25" s="2"/>
+      <c r="QN25" s="2"/>
+      <c r="QO25" s="2"/>
+      <c r="QP25" s="2"/>
+      <c r="QQ25" s="2"/>
+      <c r="QR25" s="2"/>
+      <c r="QS25" s="2"/>
+      <c r="QT25" s="2"/>
+      <c r="QU25" s="2"/>
+      <c r="QV25" s="2"/>
+      <c r="QW25" s="2"/>
+      <c r="QX25" s="2"/>
+      <c r="QY25" s="2"/>
+      <c r="QZ25" s="2"/>
+      <c r="RA25" s="2"/>
+      <c r="RB25" s="2"/>
+      <c r="RC25" s="2"/>
+      <c r="RD25" s="2"/>
+      <c r="RE25" s="2"/>
+      <c r="RF25" s="2"/>
+      <c r="RG25" s="2"/>
+      <c r="RH25" s="2"/>
+      <c r="RI25" s="2"/>
+      <c r="RJ25" s="2"/>
+      <c r="RK25" s="2"/>
+      <c r="RL25" s="2"/>
+      <c r="RM25" s="2"/>
+      <c r="RN25" s="2"/>
+      <c r="RO25" s="2"/>
+      <c r="RP25" s="2"/>
+      <c r="RQ25" s="2"/>
+      <c r="RR25" s="2"/>
+      <c r="RS25" s="2"/>
+      <c r="RT25" s="2"/>
+      <c r="RU25" s="2"/>
+      <c r="RV25" s="2"/>
+      <c r="RW25" s="2"/>
+      <c r="RX25" s="2"/>
+      <c r="RY25" s="2"/>
+      <c r="RZ25" s="2"/>
+      <c r="SA25" s="2"/>
+      <c r="SB25" s="2"/>
+      <c r="SC25" s="2"/>
+      <c r="SD25" s="2"/>
+      <c r="SE25" s="2"/>
+      <c r="SF25" s="2"/>
+      <c r="SG25" s="2"/>
+      <c r="SH25" s="2"/>
+      <c r="SI25" s="2"/>
+      <c r="SJ25" s="2"/>
+      <c r="SK25" s="2"/>
+      <c r="SL25" s="2"/>
+      <c r="SM25" s="2"/>
+      <c r="SN25" s="2"/>
+      <c r="SO25" s="2"/>
+      <c r="SP25" s="2"/>
+      <c r="SQ25" s="2"/>
+      <c r="SR25" s="2"/>
+      <c r="SS25" s="2"/>
+      <c r="ST25" s="2"/>
+      <c r="SU25" s="2"/>
+      <c r="SV25" s="2"/>
+      <c r="SW25" s="2"/>
+      <c r="SX25" s="2"/>
+      <c r="SY25" s="2"/>
+      <c r="SZ25" s="2"/>
+      <c r="TA25" s="2"/>
+      <c r="TB25" s="2"/>
+      <c r="TC25" s="2"/>
+      <c r="TD25" s="2"/>
+      <c r="TE25" s="2"/>
+      <c r="TF25" s="2"/>
+      <c r="TG25" s="2"/>
+      <c r="TH25" s="2"/>
+      <c r="TI25" s="2"/>
+      <c r="TJ25" s="2"/>
+      <c r="TK25" s="2"/>
+      <c r="TL25" s="2"/>
+      <c r="TM25" s="2"/>
+      <c r="TN25" s="2"/>
+      <c r="TO25" s="2"/>
+      <c r="TP25" s="2"/>
+      <c r="TQ25" s="2"/>
+      <c r="TR25" s="2"/>
+      <c r="TS25" s="2"/>
+      <c r="TT25" s="2"/>
+      <c r="TU25" s="2"/>
+      <c r="TV25" s="2"/>
+      <c r="TW25" s="2"/>
+      <c r="TX25" s="2"/>
+      <c r="TY25" s="2"/>
+      <c r="TZ25" s="2"/>
+      <c r="UA25" s="2"/>
+      <c r="UB25" s="2"/>
+      <c r="UC25" s="2"/>
+      <c r="UD25" s="2"/>
+      <c r="UE25" s="2"/>
+      <c r="UF25" s="2"/>
+      <c r="UG25" s="2"/>
+      <c r="UH25" s="2"/>
+      <c r="UI25" s="2"/>
+      <c r="UJ25" s="2"/>
+      <c r="UK25" s="2"/>
+      <c r="UL25" s="2"/>
+      <c r="UM25" s="2"/>
+      <c r="UN25" s="2"/>
+      <c r="UO25" s="2"/>
+      <c r="UP25" s="2"/>
+      <c r="UQ25" s="2"/>
+      <c r="UR25" s="2"/>
+      <c r="US25" s="2"/>
+      <c r="UT25" s="2"/>
+      <c r="UU25" s="2"/>
+      <c r="UV25" s="2"/>
+      <c r="UW25" s="2"/>
+      <c r="UX25" s="2"/>
+      <c r="UY25" s="2"/>
+      <c r="UZ25" s="2"/>
+      <c r="VA25" s="2"/>
+      <c r="VB25" s="2"/>
+      <c r="VC25" s="2"/>
+      <c r="VD25" s="2"/>
+      <c r="VE25" s="2"/>
+      <c r="VF25" s="2"/>
+      <c r="VG25" s="2"/>
+      <c r="VH25" s="2"/>
+      <c r="VI25" s="2"/>
+      <c r="VJ25" s="2"/>
+      <c r="VK25" s="2"/>
+      <c r="VL25" s="2"/>
+      <c r="VM25" s="2"/>
+      <c r="VN25" s="2"/>
+      <c r="VO25" s="2"/>
+      <c r="VP25" s="2"/>
+      <c r="VQ25" s="2"/>
+      <c r="VR25" s="2"/>
+      <c r="VS25" s="2"/>
+      <c r="VT25" s="2"/>
+      <c r="VU25" s="2"/>
+      <c r="VV25" s="2"/>
+      <c r="VW25" s="2"/>
+      <c r="VX25" s="2"/>
+      <c r="VY25" s="2"/>
+      <c r="VZ25" s="2"/>
+      <c r="WA25" s="2"/>
+      <c r="WB25" s="2"/>
+      <c r="WC25" s="2"/>
+      <c r="WD25" s="2"/>
+      <c r="WE25" s="2"/>
+      <c r="WF25" s="2"/>
+      <c r="WG25" s="2"/>
+      <c r="WH25" s="2"/>
+      <c r="WI25" s="2"/>
+      <c r="WJ25" s="2"/>
+      <c r="WK25" s="2"/>
+      <c r="WL25" s="2"/>
+      <c r="WM25" s="2"/>
+      <c r="WN25" s="2"/>
+      <c r="WO25" s="2"/>
+      <c r="WP25" s="2"/>
+      <c r="WQ25" s="2"/>
+      <c r="WR25" s="2"/>
+      <c r="WS25" s="2"/>
+      <c r="WT25" s="2"/>
+      <c r="WU25" s="2"/>
+      <c r="WV25" s="2"/>
+      <c r="WW25" s="2"/>
+      <c r="WX25" s="2"/>
+      <c r="WY25" s="2"/>
+      <c r="WZ25" s="2"/>
+      <c r="XA25" s="2"/>
+      <c r="XB25" s="2"/>
+      <c r="XC25" s="2"/>
+      <c r="XD25" s="2"/>
+      <c r="XE25" s="2"/>
+      <c r="XF25" s="2"/>
+      <c r="XG25" s="2"/>
+      <c r="XH25" s="2"/>
+      <c r="XI25" s="2"/>
+      <c r="XJ25" s="2"/>
+      <c r="XK25" s="2"/>
+      <c r="XL25" s="2"/>
+      <c r="XM25" s="2"/>
+      <c r="XN25" s="2"/>
+      <c r="XO25" s="2"/>
+      <c r="XP25" s="2"/>
+      <c r="XQ25" s="2"/>
+      <c r="XR25" s="2"/>
+      <c r="XS25" s="2"/>
+      <c r="XT25" s="2"/>
+      <c r="XU25" s="2"/>
+      <c r="XV25" s="2"/>
+      <c r="XW25" s="2"/>
+      <c r="XX25" s="2"/>
+      <c r="XY25" s="2"/>
+      <c r="XZ25" s="2"/>
+      <c r="YA25" s="2"/>
+      <c r="YB25" s="2"/>
+      <c r="YC25" s="2"/>
+      <c r="YD25" s="2"/>
+      <c r="YE25" s="2"/>
+      <c r="YF25" s="2"/>
+      <c r="YG25" s="2"/>
+      <c r="YH25" s="2"/>
+      <c r="YI25" s="2"/>
+      <c r="YJ25" s="2"/>
+      <c r="YK25" s="2"/>
+      <c r="YL25" s="2"/>
+      <c r="YM25" s="2"/>
+      <c r="YN25" s="2"/>
+      <c r="YO25" s="2"/>
+      <c r="YP25" s="2"/>
+      <c r="YQ25" s="2"/>
+      <c r="YR25" s="2"/>
+      <c r="YS25" s="2"/>
+      <c r="YT25" s="2"/>
+      <c r="YU25" s="2"/>
+      <c r="YV25" s="2"/>
+      <c r="YW25" s="2"/>
+      <c r="YX25" s="2"/>
+      <c r="YY25" s="2"/>
+      <c r="YZ25" s="2"/>
+      <c r="ZA25" s="2"/>
+      <c r="ZB25" s="2"/>
+      <c r="ZC25" s="2"/>
+      <c r="ZD25" s="2"/>
+      <c r="ZE25" s="2"/>
+      <c r="ZF25" s="2"/>
+      <c r="ZG25" s="2"/>
+      <c r="ZH25" s="2"/>
+      <c r="ZI25" s="2"/>
+      <c r="ZJ25" s="2"/>
+      <c r="ZK25" s="2"/>
+      <c r="ZL25" s="2"/>
+      <c r="ZM25" s="2"/>
+      <c r="ZN25" s="2"/>
+      <c r="ZO25" s="2"/>
+      <c r="ZP25" s="2"/>
+      <c r="ZQ25" s="2"/>
+      <c r="ZR25" s="2"/>
+      <c r="ZS25" s="2"/>
+      <c r="ZT25" s="2"/>
+      <c r="ZU25" s="2"/>
+      <c r="ZV25" s="2"/>
+      <c r="ZW25" s="2"/>
+      <c r="ZX25" s="2"/>
+      <c r="ZY25" s="2"/>
+      <c r="ZZ25" s="2"/>
+      <c r="AAA25" s="2"/>
+      <c r="AAB25" s="2"/>
+      <c r="AAC25" s="2"/>
+      <c r="AAD25" s="2"/>
+      <c r="AAE25" s="2"/>
+      <c r="AAF25" s="2"/>
+      <c r="AAG25" s="2"/>
+      <c r="AAH25" s="2"/>
+      <c r="AAI25" s="2"/>
+      <c r="AAJ25" s="2"/>
+      <c r="AAK25" s="2"/>
+      <c r="AAL25" s="2"/>
+      <c r="AAM25" s="2"/>
+      <c r="AAN25" s="2"/>
+      <c r="AAO25" s="2"/>
+      <c r="AAP25" s="2"/>
+      <c r="AAQ25" s="2"/>
+      <c r="AAR25" s="2"/>
+      <c r="AAS25" s="2"/>
+      <c r="AAT25" s="2"/>
+      <c r="AAU25" s="2"/>
+      <c r="AAV25" s="2"/>
+      <c r="AAW25" s="2"/>
+      <c r="AAX25" s="2"/>
+      <c r="AAY25" s="2"/>
+      <c r="AAZ25" s="2"/>
+      <c r="ABA25" s="2"/>
+      <c r="ABB25" s="2"/>
+      <c r="ABC25" s="2"/>
+      <c r="ABD25" s="2"/>
+      <c r="ABE25" s="2"/>
+      <c r="ABF25" s="2"/>
+      <c r="ABG25" s="2"/>
+      <c r="ABH25" s="2"/>
+      <c r="ABI25" s="2"/>
+      <c r="ABJ25" s="2"/>
+      <c r="ABK25" s="2"/>
+      <c r="ABL25" s="2"/>
+      <c r="ABM25" s="2"/>
+      <c r="ABN25" s="2"/>
+      <c r="ABO25" s="2"/>
+      <c r="ABP25" s="2"/>
+      <c r="ABQ25" s="2"/>
+      <c r="ABR25" s="2"/>
+      <c r="ABS25" s="2"/>
+      <c r="ABT25" s="2"/>
+      <c r="ABU25" s="2"/>
+      <c r="ABV25" s="2"/>
+      <c r="ABW25" s="2"/>
+      <c r="ABX25" s="2"/>
+      <c r="ABY25" s="2"/>
+      <c r="ABZ25" s="2"/>
+      <c r="ACA25" s="2"/>
+      <c r="ACB25" s="2"/>
+      <c r="ACC25" s="2"/>
+      <c r="ACD25" s="2"/>
+      <c r="ACE25" s="2"/>
+      <c r="ACF25" s="2"/>
+      <c r="ACG25" s="2"/>
+      <c r="ACH25" s="2"/>
+      <c r="ACI25" s="2"/>
+      <c r="ACJ25" s="2"/>
+      <c r="ACK25" s="2"/>
+      <c r="ACL25" s="2"/>
+      <c r="ACM25" s="2"/>
+      <c r="ACN25" s="2"/>
+      <c r="ACO25" s="2"/>
+      <c r="ACP25" s="2"/>
+      <c r="ACQ25" s="2"/>
+      <c r="ACR25" s="2"/>
+      <c r="ACS25" s="2"/>
+      <c r="ACT25" s="2"/>
+      <c r="ACU25" s="2"/>
+      <c r="ACV25" s="2"/>
+      <c r="ACW25" s="2"/>
+      <c r="ACX25" s="2"/>
+      <c r="ACY25" s="2"/>
+      <c r="ACZ25" s="2"/>
+      <c r="ADA25" s="2"/>
+      <c r="ADB25" s="2"/>
+      <c r="ADC25" s="2"/>
+      <c r="ADD25" s="2"/>
+      <c r="ADE25" s="2"/>
+      <c r="ADF25" s="2"/>
+      <c r="ADG25" s="2"/>
+      <c r="ADH25" s="2"/>
+      <c r="ADI25" s="2"/>
+      <c r="ADJ25" s="2"/>
+      <c r="ADK25" s="2"/>
+      <c r="ADL25" s="2"/>
+      <c r="ADM25" s="2"/>
+      <c r="ADN25" s="2"/>
+      <c r="ADO25" s="2"/>
+      <c r="ADP25" s="2"/>
+      <c r="ADQ25" s="2"/>
+      <c r="ADR25" s="2"/>
+      <c r="ADS25" s="2"/>
+      <c r="ADT25" s="2"/>
+      <c r="ADU25" s="2"/>
+      <c r="ADV25" s="2"/>
+      <c r="ADW25" s="2"/>
+      <c r="ADX25" s="2"/>
+      <c r="ADY25" s="2"/>
+      <c r="ADZ25" s="2"/>
+      <c r="AEA25" s="2"/>
+      <c r="AEB25" s="2"/>
+      <c r="AEC25" s="2"/>
+      <c r="AED25" s="2"/>
+      <c r="AEE25" s="2"/>
+      <c r="AEF25" s="2"/>
+      <c r="AEG25" s="2"/>
+      <c r="AEH25" s="2"/>
+      <c r="AEI25" s="2"/>
+      <c r="AEJ25" s="2"/>
+      <c r="AEK25" s="2"/>
+      <c r="AEL25" s="2"/>
+      <c r="AEM25" s="2"/>
+      <c r="AEN25" s="2"/>
+      <c r="AEO25" s="2"/>
+      <c r="AEP25" s="2"/>
+      <c r="AEQ25" s="2"/>
+      <c r="AER25" s="2"/>
+      <c r="AES25" s="2"/>
+      <c r="AET25" s="2"/>
+      <c r="AEU25" s="2"/>
+      <c r="AEV25" s="2"/>
+      <c r="AEW25" s="2"/>
+      <c r="AEX25" s="2"/>
+      <c r="AEY25" s="2"/>
+      <c r="AEZ25" s="2"/>
+      <c r="AFA25" s="2"/>
+      <c r="AFB25" s="2"/>
+      <c r="AFC25" s="2"/>
+      <c r="AFD25" s="2"/>
+      <c r="AFE25" s="2"/>
+      <c r="AFF25" s="2"/>
+      <c r="AFG25" s="2"/>
+      <c r="AFH25" s="2"/>
+      <c r="AFI25" s="2"/>
+      <c r="AFJ25" s="2"/>
+      <c r="AFK25" s="2"/>
+      <c r="AFL25" s="2"/>
+      <c r="AFM25" s="2"/>
+      <c r="AFN25" s="2"/>
+      <c r="AFO25" s="2"/>
+      <c r="AFP25" s="2"/>
+      <c r="AFQ25" s="2"/>
+      <c r="AFR25" s="2"/>
+      <c r="AFS25" s="2"/>
+      <c r="AFT25" s="2"/>
+      <c r="AFU25" s="2"/>
+      <c r="AFV25" s="2"/>
+      <c r="AFW25" s="2"/>
+      <c r="AFX25" s="2"/>
+      <c r="AFY25" s="2"/>
+      <c r="AFZ25" s="2"/>
+      <c r="AGA25" s="2"/>
+      <c r="AGB25" s="2"/>
+      <c r="AGC25" s="2"/>
+      <c r="AGD25" s="2"/>
+      <c r="AGE25" s="2"/>
+      <c r="AGF25" s="2"/>
+      <c r="AGG25" s="2"/>
+      <c r="AGH25" s="2"/>
+      <c r="AGI25" s="2"/>
+      <c r="AGJ25" s="2"/>
+      <c r="AGK25" s="2"/>
+      <c r="AGL25" s="2"/>
+      <c r="AGM25" s="2"/>
+      <c r="AGN25" s="2"/>
+      <c r="AGO25" s="2"/>
+      <c r="AGP25" s="2"/>
+      <c r="AGQ25" s="2"/>
+      <c r="AGR25" s="2"/>
+      <c r="AGS25" s="2"/>
+      <c r="AGT25" s="2"/>
+      <c r="AGU25" s="2"/>
+      <c r="AGV25" s="2"/>
+      <c r="AGW25" s="2"/>
+      <c r="AGX25" s="2"/>
+      <c r="AGY25" s="2"/>
+      <c r="AGZ25" s="2"/>
+      <c r="AHA25" s="2"/>
+      <c r="AHB25" s="2"/>
+      <c r="AHC25" s="2"/>
+      <c r="AHD25" s="2"/>
+      <c r="AHE25" s="2"/>
+      <c r="AHF25" s="2"/>
+      <c r="AHG25" s="2"/>
+      <c r="AHH25" s="2"/>
+      <c r="AHI25" s="2"/>
+      <c r="AHJ25" s="2"/>
+      <c r="AHK25" s="2"/>
+      <c r="AHL25" s="2"/>
+      <c r="AHM25" s="2"/>
+      <c r="AHN25" s="2"/>
+      <c r="AHO25" s="2"/>
+      <c r="AHP25" s="2"/>
+      <c r="AHQ25" s="2"/>
+      <c r="AHR25" s="2"/>
+      <c r="AHS25" s="2"/>
+      <c r="AHT25" s="2"/>
+      <c r="AHU25" s="2"/>
+      <c r="AHV25" s="2"/>
+      <c r="AHW25" s="2"/>
+      <c r="AHX25" s="2"/>
+      <c r="AHY25" s="2"/>
+      <c r="AHZ25" s="2"/>
+      <c r="AIA25" s="2"/>
+      <c r="AIB25" s="2"/>
+      <c r="AIC25" s="2"/>
+      <c r="AID25" s="2"/>
+      <c r="AIE25" s="2"/>
+      <c r="AIF25" s="2"/>
+      <c r="AIG25" s="2"/>
+      <c r="AIH25" s="2"/>
+      <c r="AII25" s="2"/>
+      <c r="AIJ25" s="2"/>
+      <c r="AIK25" s="2"/>
+      <c r="AIL25" s="2"/>
+      <c r="AIM25" s="2"/>
+      <c r="AIN25" s="2"/>
+      <c r="AIO25" s="2"/>
+      <c r="AIP25" s="2"/>
+      <c r="AIQ25" s="2"/>
+      <c r="AIR25" s="2"/>
+      <c r="AIS25" s="2"/>
+      <c r="AIT25" s="2"/>
+      <c r="AIU25" s="2"/>
+      <c r="AIV25" s="2"/>
+      <c r="AIW25" s="2"/>
+      <c r="AIX25" s="2"/>
+      <c r="AIY25" s="2"/>
+      <c r="AIZ25" s="2"/>
+      <c r="AJA25" s="2"/>
+      <c r="AJB25" s="2"/>
+      <c r="AJC25" s="2"/>
+      <c r="AJD25" s="2"/>
+      <c r="AJE25" s="2"/>
+      <c r="AJF25" s="2"/>
+      <c r="AJG25" s="2"/>
+      <c r="AJH25" s="2"/>
+      <c r="AJI25" s="2"/>
+      <c r="AJJ25" s="2"/>
+      <c r="AJK25" s="2"/>
+      <c r="AJL25" s="2"/>
+      <c r="AJM25" s="2"/>
+      <c r="AJN25" s="2"/>
+      <c r="AJO25" s="2"/>
+      <c r="AJP25" s="2"/>
+      <c r="AJQ25" s="2"/>
+      <c r="AJR25" s="2"/>
+      <c r="AJS25" s="2"/>
+      <c r="AJT25" s="2"/>
+      <c r="AJU25" s="2"/>
+      <c r="AJV25" s="2"/>
+      <c r="AJW25" s="2"/>
+      <c r="AJX25" s="2"/>
+      <c r="AJY25" s="2"/>
+      <c r="AJZ25" s="2"/>
+      <c r="AKA25" s="2"/>
+      <c r="AKB25" s="2"/>
+      <c r="AKC25" s="2"/>
+      <c r="AKD25" s="2"/>
+      <c r="AKE25" s="2"/>
+      <c r="AKF25" s="2"/>
+      <c r="AKG25" s="2"/>
+      <c r="AKH25" s="2"/>
+      <c r="AKI25" s="2"/>
+      <c r="AKJ25" s="2"/>
+      <c r="AKK25" s="2"/>
+      <c r="AKL25" s="2"/>
+      <c r="AKM25" s="2"/>
+      <c r="AKN25" s="2"/>
+      <c r="AKO25" s="2"/>
+      <c r="AKP25" s="2"/>
+      <c r="AKQ25" s="2"/>
+      <c r="AKR25" s="2"/>
+      <c r="AKS25" s="2"/>
+      <c r="AKT25" s="2"/>
+      <c r="AKU25" s="2"/>
+      <c r="AKV25" s="2"/>
+      <c r="AKW25" s="2"/>
+      <c r="AKX25" s="2"/>
+      <c r="AKY25" s="2"/>
+      <c r="AKZ25" s="2"/>
+      <c r="ALA25" s="2"/>
+      <c r="ALB25" s="2"/>
+      <c r="ALC25" s="2"/>
+      <c r="ALD25" s="2"/>
+      <c r="ALE25" s="2"/>
+      <c r="ALF25" s="2"/>
+      <c r="ALG25" s="2"/>
+      <c r="ALH25" s="2"/>
+      <c r="ALI25" s="2"/>
+      <c r="ALJ25" s="2"/>
+      <c r="ALK25" s="2"/>
+      <c r="ALL25" s="2"/>
+      <c r="ALM25" s="2"/>
+      <c r="ALN25" s="2"/>
+      <c r="ALO25" s="2"/>
+      <c r="ALP25" s="2"/>
+      <c r="ALQ25" s="2"/>
+      <c r="ALR25" s="2"/>
+      <c r="ALS25" s="2"/>
+      <c r="ALT25" s="2"/>
+      <c r="ALU25" s="2"/>
+      <c r="ALV25" s="2"/>
+      <c r="ALW25" s="2"/>
+      <c r="ALX25" s="2"/>
+      <c r="ALY25" s="2"/>
+      <c r="ALZ25" s="2"/>
+      <c r="AMA25" s="2"/>
+      <c r="AMB25" s="2"/>
+      <c r="AMC25" s="2"/>
+      <c r="AMD25" s="2"/>
+      <c r="AME25" s="2"/>
+      <c r="AMF25" s="2"/>
+      <c r="AMG25" s="2"/>
+      <c r="AMH25" s="2"/>
+      <c r="AMI25" s="2"/>
+      <c r="AMJ25" s="2"/>
+      <c r="AMK25" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:AMK8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5043,583 +7451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" customWidth="1"/>
-    <col min="5" max="1025" width="8.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="1">
-        <v>31684002</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="1">
-        <v>60881009</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="1">
-        <v>348125006</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="1">
-        <v>414428000</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="1">
-        <v>51758009</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="1">
-        <v>73572009</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="1">
-        <v>425179007</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="1">
-        <v>422107003</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="1">
-        <v>96191003</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="1">
-        <v>400786000</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="1">
-        <v>6985007</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="1">
-        <v>414984009</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="1">
-        <v>39608003</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="1">
-        <v>54544005</v>
-      </c>
-      <c r="C18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="1">
-        <v>96183007</v>
-      </c>
-      <c r="C19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="1">
-        <v>40648001</v>
-      </c>
-      <c r="C20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="1">
-        <v>85990009</v>
-      </c>
-      <c r="C21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="1">
-        <v>57811004</v>
-      </c>
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="1">
-        <v>329290002</v>
-      </c>
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="1">
-        <v>415159003</v>
-      </c>
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>65</v>
-      </c>
-      <c r="B26" s="1">
-        <v>108379008</v>
-      </c>
-      <c r="C26" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="1">
-        <v>442004000</v>
-      </c>
-      <c r="C28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="1">
-        <v>108507005</v>
-      </c>
-      <c r="C29" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="1">
-        <v>413396001</v>
-      </c>
-      <c r="C31" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="1">
-        <v>7947003</v>
-      </c>
-      <c r="C32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="1">
-        <v>412569008</v>
-      </c>
-      <c r="C33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>75</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>77</v>
-      </c>
-      <c r="B35" s="1">
-        <v>319357003</v>
-      </c>
-      <c r="C35" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" s="1">
-        <v>400487008</v>
-      </c>
-      <c r="C36" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>79</v>
-      </c>
-      <c r="B37" s="1">
-        <v>400819008</v>
-      </c>
-      <c r="C37" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>80</v>
-      </c>
-      <c r="B38" s="1">
-        <v>424102008</v>
-      </c>
-      <c r="C38" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>81</v>
-      </c>
-      <c r="B39" s="1">
-        <v>412556009</v>
-      </c>
-      <c r="C39" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" s="1">
-        <v>90332006</v>
-      </c>
-      <c r="C40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>83</v>
-      </c>
-      <c r="B41" s="1">
-        <v>423037001</v>
-      </c>
-      <c r="C41" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>84</v>
-      </c>
-      <c r="B42" s="1">
-        <v>350309002</v>
-      </c>
-      <c r="C42" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>87</v>
-      </c>
-      <c r="B44" s="1">
-        <v>423936008</v>
-      </c>
-      <c r="C44" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" s="1">
-        <v>423801005</v>
-      </c>
-      <c r="C47" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>93</v>
-      </c>
-      <c r="B48" s="1">
-        <v>400658001</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>94</v>
-      </c>
-      <c r="B49" s="1">
-        <v>427164001</v>
-      </c>
-      <c r="C49" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>95</v>
-      </c>
-      <c r="B50" s="1">
-        <v>412499001</v>
-      </c>
-      <c r="C50" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>96</v>
-      </c>
-      <c r="B51" s="1">
-        <v>398785002</v>
-      </c>
-      <c r="C51" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:AMK11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5756,7 +7588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5838,7 +7670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:AMK5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5909,7 +7741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:AMK26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6211,9 +8043,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:AMK13"/>
+  <dimension ref="A1:AMK12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" style="2" customWidth="1"/>
@@ -6344,23 +8176,12 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>571</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="C13" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6370,7 +8191,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:AMK19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6394,10 +8215,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -6405,10 +8226,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -6416,10 +8237,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
@@ -6427,10 +8248,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>4</v>
@@ -6438,10 +8259,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>4</v>
@@ -6449,10 +8270,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>4</v>
@@ -6460,10 +8281,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>4</v>
@@ -6471,10 +8292,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>4</v>
@@ -6482,10 +8303,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>4</v>
@@ -6493,10 +8314,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>4</v>
@@ -6504,10 +8325,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>39</v>
@@ -6515,10 +8336,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>39</v>
@@ -6526,10 +8347,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>4</v>
@@ -6537,10 +8358,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>4</v>
@@ -6548,10 +8369,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>4</v>
@@ -6559,10 +8380,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>4</v>
@@ -6570,10 +8391,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>4</v>
@@ -6581,10 +8402,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>4</v>
@@ -6596,7 +8417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6634,7 +8455,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6657,7 +8478,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B2" s="4">
         <v>77731008</v>
@@ -6668,10 +8489,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -6679,7 +8500,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B4" s="4">
         <v>350108002</v>
@@ -6690,10 +8511,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -6701,7 +8522,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B6" s="4">
         <v>330769006</v>
@@ -6712,7 +8533,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B7" s="4">
         <v>424378003</v>
@@ -6723,10 +8544,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C8" t="s">
         <v>39</v>
@@ -6734,10 +8555,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C9" t="s">
         <v>39</v>
@@ -6745,10 +8566,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C10" t="s">
         <v>39</v>
@@ -6756,7 +8577,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B11" s="4">
         <v>330790003</v>
@@ -6767,10 +8588,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C12" t="s">
         <v>39</v>
@@ -6778,10 +8599,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C13" t="s">
         <v>39</v>
@@ -6789,10 +8610,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C14" t="s">
         <v>39</v>
@@ -6800,10 +8621,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
@@ -6811,10 +8632,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -6822,10 +8643,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C17" t="s">
         <v>39</v>
@@ -6833,10 +8654,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C18" t="s">
         <v>39</v>
@@ -6844,10 +8665,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C19" t="s">
         <v>39</v>
@@ -6855,10 +8676,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C20" t="s">
         <v>39</v>
@@ -6866,10 +8687,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C21" t="s">
         <v>39</v>
@@ -6877,10 +8698,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C22" t="s">
         <v>39</v>
@@ -6888,10 +8709,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C23" t="s">
         <v>39</v>
@@ -6899,10 +8720,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C24" t="s">
         <v>39</v>
@@ -6910,10 +8731,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C25" t="s">
         <v>39</v>
@@ -6921,10 +8742,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C26" t="s">
         <v>39</v>
@@ -6932,10 +8753,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C27" t="s">
         <v>39</v>
@@ -6943,10 +8764,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C28" t="s">
         <v>39</v>
@@ -6954,10 +8775,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C29" t="s">
         <v>39</v>
@@ -6965,10 +8786,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C30" t="s">
         <v>39</v>
@@ -6976,10 +8797,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C31" t="s">
         <v>39</v>
@@ -6987,10 +8808,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C32" t="s">
         <v>39</v>
@@ -6998,10 +8819,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C33" t="s">
         <v>39</v>
@@ -7009,10 +8830,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C34" t="s">
         <v>39</v>
@@ -7020,10 +8841,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C35" t="s">
         <v>39</v>
@@ -7031,10 +8852,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C36" t="s">
         <v>39</v>
@@ -7042,10 +8863,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C37" t="s">
         <v>39</v>
@@ -7053,10 +8874,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C38" t="s">
         <v>39</v>
@@ -7064,10 +8885,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C39" t="s">
         <v>39</v>
@@ -7075,10 +8896,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C40" t="s">
         <v>39</v>
@@ -7086,10 +8907,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C41" t="s">
         <v>39</v>
@@ -7104,7 +8925,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:AMK4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7127,10 +8948,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -7138,10 +8959,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -7149,10 +8970,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
@@ -7164,7 +8985,360 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="1025" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="1">
+        <v>31684002</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="1">
+        <v>60881009</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="1">
+        <v>348125006</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="1">
+        <v>414428000</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="1">
+        <v>51758009</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="1">
+        <v>73572009</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="1">
+        <v>425179007</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="1">
+        <v>422107003</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="1">
+        <v>96191003</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="1">
+        <v>400786000</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="1">
+        <v>6985007</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="1">
+        <v>414984009</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="1">
+        <v>39608003</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="1">
+        <v>54544005</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="1">
+        <v>96183007</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="1">
+        <v>40648001</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="1">
+        <v>57811004</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="1">
+        <v>329290002</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="1">
+        <v>415159003</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="1">
+        <v>108379008</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="1">
+        <v>442004000</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="1">
+        <v>108507005</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1">
+        <v>413396001</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>785</v>
+      </c>
+      <c r="C31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:AMK3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7187,10 +9361,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>39</v>
@@ -7198,10 +9372,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -7213,78 +9387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" style="1" customWidth="1"/>
-    <col min="3" max="1025" width="8.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2" s="1">
-        <v>96316004</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="1">
-        <v>422170002</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" s="1">
-        <v>429833005</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:AMK9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7307,7 +9410,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B2" s="2">
         <v>108556006</v>
@@ -7318,10 +9421,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -7329,10 +9432,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
@@ -7340,10 +9443,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>4</v>
@@ -7351,10 +9454,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>4</v>
@@ -7362,10 +9465,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>4</v>
@@ -7373,10 +9476,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>4</v>
@@ -7384,10 +9487,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>4</v>
@@ -7399,9 +9502,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.85546875" bestFit="1" customWidth="1"/>
@@ -7421,7 +9524,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -7429,7 +9532,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C3" t="s">
         <v>50</v>
@@ -7437,7 +9540,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
@@ -7445,7 +9548,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C5" t="s">
         <v>50</v>
@@ -7453,7 +9556,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C6" t="s">
         <v>50</v>
@@ -7461,7 +9564,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C7" t="s">
         <v>50</v>
@@ -7469,7 +9572,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C8" t="s">
         <v>50</v>
@@ -7477,7 +9580,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C9" t="s">
         <v>50</v>
@@ -7485,7 +9588,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C10" t="s">
         <v>50</v>
@@ -7493,7 +9596,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C11" t="s">
         <v>50</v>
@@ -7501,7 +9604,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C12" t="s">
         <v>50</v>
@@ -7509,7 +9612,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C13" t="s">
         <v>50</v>
@@ -7517,7 +9620,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C14" t="s">
         <v>50</v>
@@ -7525,7 +9628,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C15" t="s">
         <v>50</v>
@@ -7533,7 +9636,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C16" t="s">
         <v>50</v>
@@ -7549,41 +9652,50 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>735</v>
-      </c>
+      <c r="A19" t="s">
+        <v>785</v>
+      </c>
+      <c r="B19" s="1"/>
       <c r="C19" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>785</v>
+      <c r="A20" s="11" t="s">
+        <v>733</v>
       </c>
       <c r="C20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>772</v>
+      <c r="A21" t="s">
+        <v>783</v>
       </c>
       <c r="C21" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>786</v>
+      <c r="A22" s="11" t="s">
+        <v>770</v>
       </c>
       <c r="C22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>784</v>
+      </c>
+      <c r="C23" t="s">
         <v>50</v>
       </c>
     </row>
@@ -7593,7 +9705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7631,7 +9743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7654,10 +9766,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -7669,7 +9781,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7730,7 +9842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7754,10 +9866,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -7769,7 +9881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7803,7 +9915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7852,7 +9964,7 @@
         <v>401</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -7864,7 +9976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7899,10 +10011,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -7910,10 +10022,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -7921,10 +10033,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -7932,10 +10044,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -7943,10 +10055,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -7954,10 +10066,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -7965,10 +10077,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -7980,7 +10092,78 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" style="1" customWidth="1"/>
+    <col min="3" max="1025" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="1">
+        <v>96316004</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="1">
+        <v>422170002</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="1">
+        <v>429833005</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8002,7 +10185,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -8014,221 +10197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" style="2" customWidth="1"/>
-    <col min="3" max="1025" width="8.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>130</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="2">
-        <v>73986003</v>
-      </c>
-      <c r="C18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8255,7 +10224,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -8263,10 +10232,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -8277,7 +10246,7 @@
         <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -8288,7 +10257,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -8307,10 +10276,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -8321,7 +10290,7 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -8329,10 +10298,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -8343,7 +10312,7 @@
         <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
@@ -8365,7 +10334,7 @@
         <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
@@ -8376,7 +10345,7 @@
         <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
@@ -8384,10 +10353,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
@@ -8395,10 +10364,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
@@ -8406,10 +10375,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
@@ -8417,10 +10386,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
@@ -8453,7 +10422,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
@@ -8461,10 +10430,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
@@ -8472,10 +10441,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
@@ -8487,7 +10456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8514,7 +10483,7 @@
         <v>194</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -8525,7 +10494,7 @@
         <v>141</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -8536,7 +10505,7 @@
         <v>140</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -8547,7 +10516,7 @@
         <v>195</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -8558,7 +10527,7 @@
         <v>137</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -8569,7 +10538,7 @@
         <v>138</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -8581,7 +10550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8605,10 +10574,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -8616,10 +10585,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -8631,7 +10600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8653,7 +10622,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -8665,7 +10634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8689,10 +10658,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -8704,7 +10673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2C00-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8731,7 +10700,7 @@
         <v>206</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -8744,6 +10713,220 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" style="2" customWidth="1"/>
+    <col min="3" max="1025" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="2">
+        <v>73986003</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9504,7 +11687,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9538,7 +11721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9774,7 +11957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10315,86 +12498,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AMK6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="26.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="2" customWidth="1"/>
-    <col min="3" max="1025" width="9.140625" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>
--- a/protected/data/dmd_data/Drug-Type-Mappings.xlsx
+++ b/protected/data/dmd_data/Drug-Type-Mappings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c58bff20204d3898/Documents/docker-compose/MM/dmd_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="11_611EE3B2B6AEC4E91FAFF6C24585CFD48B53695D" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{1884293B-2C79-480C-ACA6-99C33C7B34BC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FB4C39-CB1B-4738-8345-8352C39E7565}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="750" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15330" tabRatio="750" firstSheet="19" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Non-opioid Analgesic" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="788">
   <si>
     <t>Term</t>
   </si>
@@ -2428,6 +2428,12 @@
   </si>
   <si>
     <t>Simple Analgesics</t>
+  </si>
+  <si>
+    <t>Dexibuprofen</t>
+  </si>
+  <si>
+    <t>418027007</t>
   </si>
 </sst>
 </file>
@@ -8045,7 +8051,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:AMK12"/>
+  <dimension ref="A1:AMK13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" style="2" customWidth="1"/>
@@ -8182,6 +8188,17 @@
         <v>570</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>4</v>
       </c>
     </row>

--- a/protected/data/dmd_data/Drug-Type-Mappings.xlsx
+++ b/protected/data/dmd_data/Drug-Type-Mappings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FB4C39-CB1B-4738-8345-8352C39E7565}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5DDBFA-26F1-42B8-A601-8347BF664499}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15330" tabRatio="750" firstSheet="19" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="750" firstSheet="30" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Non-opioid Analgesic" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="790">
   <si>
     <t>Term</t>
   </si>
@@ -2434,6 +2434,12 @@
   </si>
   <si>
     <t>418027007</t>
+  </si>
+  <si>
+    <t>89519005</t>
+  </si>
+  <si>
+    <t>96067005</t>
   </si>
 </sst>
 </file>
@@ -10475,7 +10481,7 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
@@ -10558,6 +10564,28 @@
         <v>765</v>
       </c>
       <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C9" t="s">
         <v>4</v>
       </c>
     </row>

--- a/protected/data/dmd_data/Drug-Type-Mappings.xlsx
+++ b/protected/data/dmd_data/Drug-Type-Mappings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c58bff20204d3898/Documents/docker-compose/MM/dmd_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5DDBFA-26F1-42B8-A601-8347BF664499}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4B5DDBFA-26F1-42B8-A601-8347BF664499}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{543861B1-4BEF-411C-A1DF-0339F69E8756}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="750" firstSheet="30" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4635" yWindow="4635" windowWidth="28800" windowHeight="15435" tabRatio="750" firstSheet="37" activeTab="45" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Non-opioid Analgesic" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="809">
   <si>
     <t>Term</t>
   </si>
@@ -2440,6 +2440,63 @@
   </si>
   <si>
     <t>96067005</t>
+  </si>
+  <si>
+    <t>Chlortetracycline</t>
+  </si>
+  <si>
+    <t>57538001</t>
+  </si>
+  <si>
+    <t>Clobetasone + Oxytetracycline + Nystatin</t>
+  </si>
+  <si>
+    <t>35308211000001105</t>
+  </si>
+  <si>
+    <t>Demeclocycline</t>
+  </si>
+  <si>
+    <t>5737008</t>
+  </si>
+  <si>
+    <t>10504007</t>
+  </si>
+  <si>
+    <t>Lymecycline</t>
+  </si>
+  <si>
+    <t>96077007</t>
+  </si>
+  <si>
+    <t>Minocycline</t>
+  </si>
+  <si>
+    <t>13512003</t>
+  </si>
+  <si>
+    <t>Oxytetracycline</t>
+  </si>
+  <si>
+    <t>22969001</t>
+  </si>
+  <si>
+    <t>Oxytetracycline + Hydrocortisone</t>
+  </si>
+  <si>
+    <t>346509004</t>
+  </si>
+  <si>
+    <t>Tigecycline</t>
+  </si>
+  <si>
+    <t>418631002</t>
+  </si>
+  <si>
+    <t>Triamcinolone + Chlortetracycline</t>
+  </si>
+  <si>
+    <t>346689008</t>
   </si>
 </sst>
 </file>
@@ -2502,7 +2559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2523,6 +2580,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10720,7 +10778,7 @@
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2C00-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
@@ -10733,7 +10791,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -10742,12 +10800,122 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>791</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>792</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>794</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>795</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>796</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>797</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>798</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>799</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>801</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>803</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>804</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>206</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B10" s="12" t="s">
         <v>773</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>805</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>807</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>808</v>
+      </c>
+      <c r="C12" t="s">
         <v>4</v>
       </c>
     </row>

--- a/protected/data/dmd_data/Drug-Type-Mappings.xlsx
+++ b/protected/data/dmd_data/Drug-Type-Mappings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c58bff20204d3898/Documents/docker-compose/MM/dmd_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FB4C39-CB1B-4738-8345-8352C39E7565}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4B5DDBFA-26F1-42B8-A601-8347BF664499}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{543861B1-4BEF-411C-A1DF-0339F69E8756}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15330" tabRatio="750" firstSheet="19" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4635" yWindow="4635" windowWidth="28800" windowHeight="15435" tabRatio="750" firstSheet="37" activeTab="45" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Non-opioid Analgesic" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="809">
   <si>
     <t>Term</t>
   </si>
@@ -2434,6 +2434,69 @@
   </si>
   <si>
     <t>418027007</t>
+  </si>
+  <si>
+    <t>89519005</t>
+  </si>
+  <si>
+    <t>96067005</t>
+  </si>
+  <si>
+    <t>Chlortetracycline</t>
+  </si>
+  <si>
+    <t>57538001</t>
+  </si>
+  <si>
+    <t>Clobetasone + Oxytetracycline + Nystatin</t>
+  </si>
+  <si>
+    <t>35308211000001105</t>
+  </si>
+  <si>
+    <t>Demeclocycline</t>
+  </si>
+  <si>
+    <t>5737008</t>
+  </si>
+  <si>
+    <t>10504007</t>
+  </si>
+  <si>
+    <t>Lymecycline</t>
+  </si>
+  <si>
+    <t>96077007</t>
+  </si>
+  <si>
+    <t>Minocycline</t>
+  </si>
+  <si>
+    <t>13512003</t>
+  </si>
+  <si>
+    <t>Oxytetracycline</t>
+  </si>
+  <si>
+    <t>22969001</t>
+  </si>
+  <si>
+    <t>Oxytetracycline + Hydrocortisone</t>
+  </si>
+  <si>
+    <t>346509004</t>
+  </si>
+  <si>
+    <t>Tigecycline</t>
+  </si>
+  <si>
+    <t>418631002</t>
+  </si>
+  <si>
+    <t>Triamcinolone + Chlortetracycline</t>
+  </si>
+  <si>
+    <t>346689008</t>
   </si>
 </sst>
 </file>
@@ -2496,7 +2559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2517,6 +2580,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10475,7 +10539,7 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
@@ -10558,6 +10622,28 @@
         <v>765</v>
       </c>
       <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C9" t="s">
         <v>4</v>
       </c>
     </row>
@@ -10692,7 +10778,7 @@
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2C00-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
@@ -10705,7 +10791,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -10714,12 +10800,122 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>791</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>792</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>794</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>795</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>796</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>797</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>798</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>799</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>801</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>803</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>804</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>206</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B10" s="12" t="s">
         <v>773</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>805</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>807</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>808</v>
+      </c>
+      <c r="C12" t="s">
         <v>4</v>
       </c>
     </row>
